--- a/financial_models/opportunities/1368.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1368.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{506166D0-7312-48F9-A01D-1DF5418E42CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B416D751-5D4A-4BF8-B352-27DCCD06F2B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,6 +5025,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5034,16 +5043,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>349</v>
       </c>
       <c r="C8" s="47">
-        <v>4.5</v>
+        <v>4.63</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>12627.325602000001</v>
+        <v>12992.11500828</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.17507743819135022</v>
+        <v>0.18450387130746587</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>354</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>353</v>
       </c>
       <c r="E16" s="416">
-        <v>1.08</v>
+        <v>1.1456630000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>6.3236298929310664</v>
+        <v>6.7081007352084114</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>346</v>
@@ -5561,13 +5561,13 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>3.4173243414630332</v>
+        <v>3.5527313314558078</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>405</v>
       </c>
       <c r="E22" s="79">
-        <v>0.29465259038036601</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5576,13 +5576,13 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>4.231239290802141</v>
+        <v>4.4612851476900524</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>406</v>
       </c>
       <c r="E23" s="443">
-        <v>0.20075184365903001</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>5.1959933069705535</v>
+        <v>5.4715667789839957</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>407</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>5.844355259741115</v>
+        <v>6.156008399483123</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>408</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>8.4793915239875603E-2</v>
+        <v>8.7423732285332623E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.1111111111111116E-2</v>
+        <v>5.9395248380129599E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>477</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-1.042909785894345</v>
+        <v>-1.1063177352195119</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.72979019375578791</v>
+        <v>0.7741607618044789</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.28105728717709516</v>
+        <v>0.29814530999923367</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>-3.2062304961461882E-2</v>
+        <v>-3.4011663415799351E-2</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>484</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>482</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>0.81561021015952773</v>
+        <v>0.86519855574258797</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>7.3813485702962334</v>
+        <v>7.8301277287882352</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>490</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>7.71 HKD</v>
+        <v>8.18 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-2.5962898620842893E-2</v>
+        <v>-2.8142121143173257E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>6.63 HKD</v>
+        <v>7.03 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.6668609069817772E-2</v>
+        <v>2.4254482087399148E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>6.14 HKD</v>
+        <v>6.52 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.4038831640183929E-2</v>
+        <v>5.1496390427895715E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>5.7 HKD</v>
+        <v>6.04 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>8.2120404534868074E-2</v>
+        <v>7.9441845632736027E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>5.28 HKD</v>
+        <v>5.6 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.11091778888498864</v>
+        <v>0.10809486889244155</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>6.3236298929310664</v>
+        <v>6.7081007352084114</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>358</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6585,19 +6585,19 @@
       </c>
       <c r="C140" s="333">
         <f>Scenarios!C62</f>
-        <v>0.50320918343028298</v>
+        <v>0.49943104233045083</v>
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>2.9141151580327502</v>
+        <v>3.0533002891253571</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>3.4173243414630332</v>
+        <v>3.5527313314558078</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6606,19 +6606,19 @@
       </c>
       <c r="C141" s="333">
         <f>Scenarios!C63</f>
-        <v>0.5786010854989968</v>
+        <v>0.57928240740740733</v>
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>3.6526382053031443</v>
+        <v>3.8820027402826454</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>4.231239290802141</v>
+        <v>4.4612851476900524</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>4.5325274473374249</v>
+        <v>4.808100919350867</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>5.1959933069705535</v>
+        <v>5.4715667789839957</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>5.1259520722685359</v>
+        <v>5.4376052120105438</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>5.844355259741115</v>
+        <v>6.156008399483123</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>359</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>437</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,6 +6796,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6812,18 +6824,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -9946,11 +9946,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.9267429496033994</v>
+        <v>4.1654852850661843</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>0.81561021015952773</v>
+        <v>0.86519855574258797</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10356,11 +10356,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-2926480.3200000003</v>
+        <v>-3104407.613752</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-1.042909785894345</v>
+        <v>-1.1063177352195119</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10373,11 +10373,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>2047844.0883780003</v>
+        <v>2172351.1127994489</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.72979019375578791</v>
+        <v>0.7741607618044789</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10390,11 +10390,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>788667.08400000015</v>
+        <v>836617.31245990016</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.28105728717709522</v>
+        <v>0.29814530999923372</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10407,11 +10407,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>-89969.147621999844</v>
+        <v>-95439.188492650981</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>-3.2062304961461896E-2</v>
+        <v>-3.4011663415799309E-2</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -13994,16 +13994,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.1111111111111116E-2</v>
+        <v>5.9395248380129599E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.1111111111111116E-2</v>
+        <v>5.9395248380129599E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.577777777777778E-2</v>
+        <v>5.4211663066954643E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15158,18 +15158,18 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.38157261857944025</v>
+        <v>0.40477188048109003</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.30780861304347634</v>
+        <v>0.32652309170854471</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.33733811531123614</v>
+        <v>0.35784796037205252</v>
       </c>
       <c r="I123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15215,18 +15215,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.4793915239875603E-2</v>
+        <v>8.7423732285332623E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.8401914009661405E-2</v>
+        <v>7.0523345941370344E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.4964025624719141E-2</v>
+        <v>7.7288976322257563E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15272,11 +15272,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10861927879508876</v>
+        <v>0.10556949342935193</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10338721287057218</v>
+        <v>0.10048433216362308</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16197,7 +16197,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>-3.2062304961461882E-2</v>
+        <v>-3.4011663415799351E-2</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.08</v>
+        <v>1.1456630000000001</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16247,7 +16247,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>20712598.173108384</v>
+        <v>21971904.963701732</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16269,7 +16269,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>7.3813485702962334</v>
+        <v>7.8301277287882352</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16392,7 +16392,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>6.3251389761285743</v>
+        <v>6.7097015692670281</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18580,23 +18580,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>7.3813485702962334</v>
+        <v>7.8301277287882352</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>7.3813485702962334</v>
+        <v>7.8301277287882352</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>7.3813485702962334</v>
+        <v>7.8301277287882352</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>7.3813485702962334</v>
+        <v>7.8301277287882352</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>7.3813485702962334</v>
+        <v>7.8301277287882352</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18611,23 +18611,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>5.329154134849337</v>
+        <v>5.6531617718462002</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>5.3827662992474439</v>
+        <v>5.710033506198819</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>5.4363784636455526</v>
+        <v>5.7669052405514396</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>5.4899906280436612</v>
+        <v>5.8237769749040602</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>5.5972149568398768</v>
+        <v>5.9375204436092996</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18642,23 +18642,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>5.3225195676634707</v>
+        <v>5.6461238291185509</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>5.4265532987832747</v>
+        <v>5.7564827147629103</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>5.5315867905445364</v>
+        <v>5.8679021455700227</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>5.6376200429472565</v>
+        <v>5.9803821215398916</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>5.852685829677065</v>
+        <v>6.208523708967884</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18673,23 +18673,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>5.3163334910332907</v>
+        <v>5.6395616447571051</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>5.4677886083694656</v>
+        <v>5.8002250929910995</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>5.6221345699729435</v>
+        <v>5.963955146147141</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>5.77939934117635</v>
+        <v>6.1307814698241856</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>6.1027971737134692</v>
+        <v>6.4738415911371243</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18704,23 +18704,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>5.3105655874154065</v>
+        <v>5.6334430579399051</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>5.5066209278865292</v>
+        <v>5.8414183815789489</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>5.7082499406181384</v>
+        <v>6.0553062515911096</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>5.9155603455362247</v>
+        <v>6.2752209371741374</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>6.3476614266162441</v>
+        <v>6.7335933638902281</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18735,23 +18735,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>5.3051875887040945</v>
+        <v>5.627738081886573</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>5.5431902917207809</v>
+        <v>5.8802111288738006</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>5.7901498735394448</v>
+        <v>6.1421856246007609</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>6.046325692380675</v>
+        <v>6.4139366960277044</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>6.5873886672203588</v>
+        <v>6.9878957987534056</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18766,23 +18766,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>5.3001731376912158</v>
+        <v>5.6224187568951223</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>5.5776285737465097</v>
+        <v>5.9167432265593956</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>5.868040718835231</v>
+        <v>6.2248121611693765</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>6.1719091956438756</v>
+        <v>6.5471555600082869</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>6.8220866650145995</v>
+        <v>7.2368632175005745</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18798,23 +18798,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>5.2954976588913292</v>
+        <v>5.6174590133133488</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>5.610059962880297</v>
+        <v>5.9511464141234534</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>5.9421187255501051</v>
+        <v>6.3033940421017691</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>6.2925161964467637</v>
+        <v>6.6750953547868415</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>7.0518609285893774</v>
+        <v>7.4806075435467525</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18829,23 +18829,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>5.2911382380988927</v>
+        <v>5.6128345437732339</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>5.6406014109223719</v>
+        <v>5.9835447539273678</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>6.0125705361320838</v>
+        <v>6.3781292575339741</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>6.4083438988495365</v>
+        <v>6.7979652742478294</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>7.2768147530681828</v>
+        <v>7.7192383522632904</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18861,23 +18861,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>5.2870735100872981</v>
+        <v>5.6085226840621711</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>5.6693630542999891</v>
+        <v>6.014055078591193</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>6.0795736566855725</v>
+        <v>6.4492061057771881</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>6.5195816922992869</v>
+        <v>6.9159662225413685</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>7.4970492665439359</v>
+        <v>7.9528629202375232</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18893,23 +18893,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>5.2832835538993308</v>
+        <v>5.6045023020471945</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>5.6964486112336896</v>
+        <v>6.0427874123072431</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>6.1432969042049761</v>
+        <v>6.5168036677427645</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>6.6264114612999778</v>
+        <v>7.0292911425808491</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>7.712663475541178</v>
+        <v>8.1815862734990112</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18925,23 +18925,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>5.2678474527200683</v>
+        <v>5.5881277002089185</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>5.8099613033752524</v>
+        <v>6.1632015710266685</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>6.4180672836565051</v>
+        <v>6.808279831847929</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>7.1003170501250823</v>
+        <v>7.5320097524050489</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>8.724752202250734</v>
+        <v>9.2552090576733175</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -18957,23 +18957,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>5.2569694011765851</v>
+        <v>5.5765882732038614</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>5.8940358992482649</v>
+        <v>6.2523878244819118</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>6.6318557481429679</v>
+        <v>7.0350664370228859</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>7.4874779134885658</v>
+        <v>7.9427096377787514</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>9.6350397010539037</v>
+        <v>10.220841193544924</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -18989,23 +18989,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>5.249303475434818</v>
+        <v>5.5684562662750743</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>5.9563068007470612</v>
+        <v>6.3184447391335929</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>6.7981964855933148</v>
+        <v>7.2115205372910127</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>7.803771997489501</v>
+        <v>8.2782341092220513</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>10.453765676958508</v>
+        <v>11.089344950704922</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19021,23 +19021,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>5.2439011828235556</v>
+        <v>5.562725519275169</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>6.0024285231675867</v>
+        <v>6.3673706195719877</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>6.9276199369567415</v>
+        <v>7.3488128146608069</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>8.0621709139111388</v>
+        <v>8.5523434405038667</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>11.190139871377589</v>
+        <v>11.870490014316726</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19084,7 +19084,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>7.712663475541178</v>
+        <v>8.1815862734990112</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19112,7 +19112,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>6.6264114612999778</v>
+        <v>7.0292911425808491</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19140,7 +19140,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>6.1432969042049761</v>
+        <v>6.5168036677427645</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19168,7 +19168,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>5.6964486112336896</v>
+        <v>6.0427874123072431</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19196,7 +19196,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>5.2832835538993308</v>
+        <v>5.6045023020471945</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19556,7 +19556,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>6.6264114612999778</v>
+        <v>7.0292911425808491</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19580,7 +19580,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>6.1432969042049761</v>
+        <v>6.5168036677427645</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19603,7 +19603,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>5.6964486112336896</v>
+        <v>6.0427874123072431</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19619,7 +19619,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>6.1282077423811554</v>
+        <v>6.5007970988515016</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19666,7 +19666,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>7.712663475541178</v>
+        <v>8.1815862734990112</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19689,7 +19689,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>5.2832835538993308</v>
+        <v>5.6045023020471945</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19734,7 +19734,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.5</v>
+        <v>4.63</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.17507743819135022</v>
+        <v>0.18450387130746587</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>7.3813485702962334</v>
+        <v>7.8301277287882352</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19765,7 +19765,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>-1.1040571761082373E-2</v>
+        <v>-1.3284833588145683E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19774,7 +19774,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>6.3236298929310664</v>
+        <v>6.7081007352084114</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>6.3251389761285743</v>
+        <v>6.7097015692670281</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19944,7 +19944,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>-5.0702374276051588E-3</v>
+        <v>-5.0702374276051501E-3</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20018,23 +20018,23 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>0.50320918343028298</v>
+        <v>0.49943104233045083</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>2.9141151580327502</v>
+        <v>3.0533002891253571</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>3.4173243414630332</v>
+        <v>3.5527313314558078</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.3</v>
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.45959450516180211</v>
+        <v>0.47038193496278358</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20043,23 +20043,23 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>0.5786010854989968</v>
+        <v>0.57928240740740733</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>3.6526382053031443</v>
+        <v>3.8820027402826454</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>4.231239290802141</v>
+        <v>4.4612851476900524</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.2</v>
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.33088441884746056</v>
+        <v>0.33494064508089916</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20093,11 +20093,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>4.5325274473374249</v>
+        <v>4.808100919350867</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>5.1959933069705535</v>
+        <v>5.4715667789839957</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20105,7 +20105,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.17832109169150667</v>
+        <v>0.18433443459402643</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20118,11 +20118,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>5.1259520722685359</v>
+        <v>5.4376052120105438</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>5.844355259741115</v>
+        <v>6.156008399483123</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>7.5791063250825852E-2</v>
+        <v>8.2302332287223168E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.5</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20259,14 +20259,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>12627.325602000001</v>
+        <v>12992.11500828</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.17507743819135022</v>
+        <v>0.18450387130746587</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20274,13 +20274,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20318,7 +20318,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.08</v>
+        <v>1.1456630000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20344,7 +20344,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>6.3236298929310664</v>
+        <v>6.7081007352084114</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>361</v>
@@ -20396,14 +20396,14 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>3.4173243414630332</v>
+        <v>3.5527313314558078</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>439</v>
       </c>
       <c r="E22" s="366">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20412,14 +20412,14 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>4.231239290802141</v>
+        <v>4.4612851476900524</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>440</v>
       </c>
       <c r="E23" s="368">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20428,7 +20428,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>5.1959933069705535</v>
+        <v>5.4715667789839957</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>442</v>
@@ -20444,7 +20444,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>5.844355259741115</v>
+        <v>6.156008399483123</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>441</v>
@@ -20465,22 +20465,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20670,10 +20670,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20689,22 +20689,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20738,7 +20738,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>8.4793915239875603E-2</v>
+        <v>8.7423732285332623E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20748,7 +20748,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>6.1111111111111116E-2</v>
+        <v>5.9395248380129599E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>372</v>
@@ -20839,22 +20839,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>478</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20862,13 +20862,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -20889,7 +20889,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-1.042909785894345</v>
+        <v>-1.1063177352195119</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -20951,7 +20951,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.72979019375578791</v>
+        <v>0.7741607618044789</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -20982,7 +20982,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.28105728717709516</v>
+        <v>0.29814530999923367</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -20995,7 +20995,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>-3.2062304961461882E-2</v>
+        <v>-3.4011663415799351E-2</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21017,33 +21017,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21106,23 +21106,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21140,7 +21140,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>0.81561021015952773</v>
+        <v>0.86519855574258797</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21154,7 +21154,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>7.3813485702962334</v>
+        <v>7.8301277287882352</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21166,13 +21166,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>7.71 HKD</v>
+        <v>8.18 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21240,7 +21240,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>6.63 HKD</v>
+        <v>7.03 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21262,7 +21262,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>6.14 HKD</v>
+        <v>6.52 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21284,7 +21284,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>5.7 HKD</v>
+        <v>6.04 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21306,7 +21306,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>5.28 HKD</v>
+        <v>5.6 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21328,7 +21328,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>6.3236298929310664</v>
+        <v>6.7081007352084114</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21336,13 +21336,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21355,22 +21355,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21431,19 +21431,19 @@
       </c>
       <c r="C140" s="409">
         <f>Scenarios!C62</f>
-        <v>0.50320918343028298</v>
+        <v>0.49943104233045083</v>
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>2.9141151580327502</v>
+        <v>3.0533002891253571</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>3.4173243414630332</v>
+        <v>3.5527313314558078</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21452,19 +21452,19 @@
       </c>
       <c r="C141" s="409">
         <f>Scenarios!C63</f>
-        <v>0.5786010854989968</v>
+        <v>0.57928240740740733</v>
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>3.6526382053031443</v>
+        <v>3.8820027402826454</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>4.231239290802141</v>
+        <v>4.4612851476900524</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21496,11 +21496,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>4.5325274473374249</v>
+        <v>4.808100919350867</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>5.1959933069705535</v>
+        <v>5.4715667789839957</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21517,11 +21517,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>5.1259520722685359</v>
+        <v>5.4376052120105438</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>5.844355259741115</v>
+        <v>6.156008399483123</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21539,13 +21539,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21553,13 +21553,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21596,22 +21596,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>387</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21635,12 +21635,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21655,15 +21658,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/1368.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1368.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B416D751-5D4A-4BF8-B352-27DCCD06F2B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CC27906-2286-452F-9CE1-E0F17C730755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,25 +5025,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>349</v>
       </c>
       <c r="C8" s="47">
-        <v>4.63</v>
+        <v>4.5599999999999996</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>12992.11500828</v>
+        <v>12795.689943359999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.18450387130746587</v>
+        <v>0.19114376894438945</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>354</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>353</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1456630000000001</v>
+        <v>1.14663</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>6.7081007352084114</v>
+        <v>6.7137627260477304</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>346</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>3.5527313314558078</v>
+        <v>3.5553084779461672</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>405</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>4.4612851476900524</v>
+        <v>4.4645617627591028</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>406</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>5.4715667789839957</v>
+        <v>5.4756250697632325</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>407</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>6.156008399483123</v>
+        <v>6.1605980250885715</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>408</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>8.7423732285332623E-2</v>
+        <v>8.884068624954182E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>5.9395248380129599E-2</v>
+        <v>6.0307017543859656E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>477</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-1.1063177352195119</v>
+        <v>-1.1072515257407711</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.7741607618044789</v>
+        <v>0.77481419432055476</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.29814530999923367</v>
+        <v>0.29839696036654872</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>-3.4011663415799351E-2</v>
+        <v>-3.4040371053667626E-2</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>482</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>0.86519855574258797</v>
+        <v>0.86592882895853629</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>7.8301277287882352</v>
+        <v>7.8367367695914547</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>490</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.18 HKD</v>
+        <v>8.19 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-2.8142121143173257E-2</v>
+        <v>-2.8172352000014306E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>7.03 HKD</v>
+        <v>7.04 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.4254482087399148E-2</v>
+        <v>2.4220995039074499E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.1496390427895715E-2</v>
+        <v>5.1461124895888617E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>6.04 HKD</v>
+        <v>6.05 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>7.9441845632736027E-2</v>
+        <v>7.9404693593109255E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>5.6 HKD</v>
+        <v>5.61 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.10809486889244155</v>
+        <v>0.10805571624597797</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>356</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>6.7081007352084114</v>
+        <v>6.7137627260477304</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>358</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>3.0533002891253571</v>
+        <v>3.0558774356157166</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>3.5527313314558078</v>
+        <v>3.5553084779461672</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6610,11 +6610,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>3.8820027402826454</v>
+        <v>3.8852793553516958</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>4.4612851476900524</v>
+        <v>4.4645617627591028</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>4.808100919350867</v>
+        <v>4.8121592101301038</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>5.4715667789839957</v>
+        <v>5.4756250697632325</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>5.4376052120105438</v>
+        <v>5.4421948376159923</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>6.156008399483123</v>
+        <v>6.1605980250885715</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>437</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,18 +6796,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6824,6 +6812,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -9946,11 +9946,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>4.1654852850661843</v>
+        <v>4.1690011743553201</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>0.86519855574258797</v>
+        <v>0.86592882895853629</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10356,11 +10356,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-3104407.613752</v>
+        <v>-3107027.8975200001</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-1.1063177352195119</v>
+        <v>-1.1072515257407711</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10373,11 +10373,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>2172351.1127994489</v>
+        <v>2174184.6917193206</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.7741607618044789</v>
+        <v>0.77481419432055476</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10390,11 +10390,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>836617.31245990016</v>
+        <v>837323.46159900003</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.29814530999923372</v>
+        <v>0.29839696036654872</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10407,11 +10407,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>-95439.188492650981</v>
+        <v>-95519.744201679481</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>-3.4011663415799309E-2</v>
+        <v>-3.404037105366764E-2</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -13994,16 +13994,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.9395248380129599E-2</v>
+        <v>6.0307017543859656E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.9395248380129599E-2</v>
+        <v>6.0307017543859656E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.4211663066954643E-2</v>
+        <v>5.5043859649122812E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15158,18 +15158,18 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.40477188048109003</v>
+        <v>0.40511352929791067</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.32652309170854471</v>
+        <v>0.3267986944204086</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.35784796037205252</v>
+        <v>0.3581500029252988</v>
       </c>
       <c r="I123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15215,18 +15215,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.7423732285332623E-2</v>
+        <v>8.884068624954182E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.0523345941370344E-2</v>
+        <v>7.1666380355352763E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.7288976322257563E-2</v>
+        <v>7.8541667308179575E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15272,11 +15272,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10556949342935193</v>
+        <v>0.10719007775831128</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10048433216362308</v>
+        <v>0.10202685480648571</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16197,7 +16197,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>-3.4011663415799351E-2</v>
+        <v>-3.4040371053667626E-2</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1456630000000001</v>
+        <v>1.14663</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16247,7 +16247,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>21971904.963701732</v>
+        <v>21990450.410399321</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16269,7 +16269,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>7.8301277287882352</v>
+        <v>7.8367367695914547</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16392,7 +16392,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>6.7097015692670281</v>
+        <v>6.7153649112947269</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18580,23 +18580,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>7.8301277287882352</v>
+        <v>7.8367367695914547</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>7.8301277287882352</v>
+        <v>7.8367367695914547</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>7.8301277287882352</v>
+        <v>7.8367367695914547</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>7.8301277287882352</v>
+        <v>7.8367367695914547</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>7.8301277287882352</v>
+        <v>7.8367367695914547</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18611,23 +18611,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>5.6531617718462002</v>
+        <v>5.6579333385576804</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>5.710033506198819</v>
+        <v>5.7148530756537923</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>5.7669052405514396</v>
+        <v>5.7717728127499068</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>5.8237769749040602</v>
+        <v>5.8286925498460214</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>5.9375204436092996</v>
+        <v>5.9425320240382478</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18642,23 +18642,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>5.6461238291185509</v>
+        <v>5.650889455435153</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>5.7564827147629103</v>
+        <v>5.761341489799876</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>5.8679021455700227</v>
+        <v>5.872854964483408</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>5.9803821215398916</v>
+        <v>5.9854298794857526</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>6.208523708967884</v>
+        <v>6.2137640304468631</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18673,23 +18673,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>5.6395616447571051</v>
+        <v>5.6443217322439834</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>5.8002250929910995</v>
+        <v>5.8051207889024816</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>5.963955146147141</v>
+        <v>5.9689890388593287</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>6.1307814698241856</v>
+        <v>6.1359561727528131</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>6.4738415911371243</v>
+        <v>6.4793058549028473</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18704,23 +18704,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>5.6334430579399051</v>
+        <v>5.638197981016785</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>5.8414183815789489</v>
+        <v>5.8463488467986391</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>6.0553062515911096</v>
+        <v>6.0604172494546074</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>6.2752209371741374</v>
+        <v>6.2805175546316674</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>6.7335933638902281</v>
+        <v>6.7392768718527627</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18735,23 +18735,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>5.627738081886573</v>
+        <v>5.6324881896627552</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>5.8802111288738006</v>
+        <v>5.8851743372183325</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>6.1421856246007609</v>
+        <v>6.147369953237531</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>6.4139366960277044</v>
+        <v>6.4193503969022716</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>6.9878957987534056</v>
+        <v>6.9937939513841485</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18766,23 +18766,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>5.6224187568951223</v>
+        <v>5.6271643748804436</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>5.9167432265593956</v>
+        <v>5.9217372699212589</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>6.2248121611693765</v>
+        <v>6.2300662309611488</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>6.5471555600082869</v>
+        <v>6.5526817046306824</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>7.2368632175005745</v>
+        <v>7.2429715117645275</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18798,23 +18798,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>5.6174590133133488</v>
+        <v>5.6222004450134859</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>5.9511464141234534</v>
+        <v>5.9561694955902178</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>6.3033940421017691</v>
+        <v>6.3087144391458496</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>6.6750953547868415</v>
+        <v>6.6807294873442151</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>7.4806075435467525</v>
+        <v>7.4869215708781836</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18829,23 +18829,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>5.6128345437732339</v>
+        <v>5.6175720721771603</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>5.9835447539273678</v>
+        <v>5.9885951813017764</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>6.3781292575339741</v>
+        <v>6.3835127350417888</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>6.7979652742478294</v>
+        <v>6.8037031154980028</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>7.7192383522632904</v>
+        <v>7.7257537965838612</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18861,23 +18861,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>5.6085226840621711</v>
+        <v>5.6132565730290729</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>6.014055078591193</v>
+        <v>6.0191312582888852</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>6.4492061057771881</v>
+        <v>6.4546495758938685</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>6.9159662225413685</v>
+        <v>6.9218036628158623</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>7.9528629202375232</v>
+        <v>7.9595755560159933</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18893,23 +18893,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>5.6045023020471945</v>
+        <v>5.6092327975996206</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>6.0427874123072431</v>
+        <v>6.0478878436100789</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>6.5168036677427645</v>
+        <v>6.5223041937671775</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>7.0292911425808491</v>
+        <v>7.0352242350651792</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>8.1815862734990112</v>
+        <v>8.1884919638516482</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18925,23 +18925,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>5.5881277002089185</v>
+        <v>5.5928443747337147</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>6.1632015710266685</v>
+        <v>6.1684036382307088</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>6.808279831847929</v>
+        <v>6.8140263791287579</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>7.5320097524050489</v>
+        <v>7.538367165911966</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>9.2552090576733175</v>
+        <v>9.2630209422840366</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -18957,23 +18957,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>5.5765882732038614</v>
+        <v>5.5812952078436187</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>6.2523878244819118</v>
+        <v>6.2576651695879972</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>7.0350664370228859</v>
+        <v>7.0410044041603435</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>7.9427096377787514</v>
+        <v>7.9494137036512909</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>10.220841193544924</v>
+        <v>10.229468122610591</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -18989,23 +18989,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>5.5684562662750743</v>
+        <v>5.5731563370720609</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>6.3184447391335929</v>
+        <v>6.323777839759817</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>7.2115205372910127</v>
+        <v>7.2176074409961686</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>8.2782341092220513</v>
+        <v>8.2852213754457278</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>11.089344950704922</v>
+        <v>11.098704942750864</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19021,23 +19021,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>5.562725519275169</v>
+        <v>5.5674207530194195</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>6.3673706195719877</v>
+        <v>6.3727450162218977</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>7.3488128146608069</v>
+        <v>7.355015600289545</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>8.5523434405038667</v>
+        <v>8.5595620694610446</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>11.870490014316726</v>
+        <v>11.880509333997857</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19084,7 +19084,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>8.1815862734990112</v>
+        <v>8.1884919638516482</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19112,7 +19112,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>7.0292911425808491</v>
+        <v>7.0352242350651792</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19140,7 +19140,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>6.5168036677427645</v>
+        <v>6.5223041937671775</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19168,7 +19168,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>6.0427874123072431</v>
+        <v>6.0478878436100789</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19196,7 +19196,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>5.6045023020471945</v>
+        <v>5.6092327975996206</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19556,7 +19556,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>7.0292911425808491</v>
+        <v>7.0352242350651792</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19580,7 +19580,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>6.5168036677427645</v>
+        <v>6.5223041937671775</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19603,7 +19603,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>6.0427874123072431</v>
+        <v>6.0478878436100789</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19619,7 +19619,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>6.5007970988515016</v>
+        <v>6.5062841144875039</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19666,7 +19666,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>8.1815862734990112</v>
+        <v>8.1884919638516482</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19689,7 +19689,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>5.6045023020471945</v>
+        <v>5.6092327975996206</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19734,7 +19734,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.63</v>
+        <v>4.5599999999999996</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.18450387130746587</v>
+        <v>0.19114376894438945</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>7.8301277287882352</v>
+        <v>7.8367367695914547</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19765,7 +19765,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>-1.3284833588145683E-2</v>
+        <v>-1.3315966047741299E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19774,7 +19774,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>6.7081007352084114</v>
+        <v>6.7137627260477304</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>6.7097015692670281</v>
+        <v>6.7153649112947269</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19944,7 +19944,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>-5.0702374276051501E-3</v>
+        <v>-5.0702374276051579E-3</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20022,11 +20022,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>3.0533002891253571</v>
+        <v>3.0558774356157166</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>3.5527313314558078</v>
+        <v>3.5553084779461672</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20034,7 +20034,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.47038193496278358</v>
+        <v>0.47044472332147602</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20047,11 +20047,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>3.8820027402826454</v>
+        <v>3.8852793553516958</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>4.4612851476900524</v>
+        <v>4.4645617627591028</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.33494064508089916</v>
+        <v>0.33501347233531009</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20093,11 +20093,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>4.808100919350867</v>
+        <v>4.8121592101301038</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>5.4715667789839957</v>
+        <v>5.4756250697632325</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20105,7 +20105,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.18433443459402643</v>
+        <v>0.18441784537318118</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20118,11 +20118,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>5.4376052120105438</v>
+        <v>5.4421948376159923</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>6.156008399483123</v>
+        <v>6.1605980250885715</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>8.2302332287223168E-2</v>
+        <v>8.2392649774919446E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.63</v>
+        <v>4.5599999999999996</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20259,14 +20259,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>12992.11500828</v>
+        <v>12795.689943359999</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.18450387130746587</v>
+        <v>0.19114376894438945</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20274,13 +20274,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20318,7 +20318,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1456630000000001</v>
+        <v>1.14663</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20344,7 +20344,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>6.7081007352084114</v>
+        <v>6.7137627260477304</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>361</v>
@@ -20396,7 +20396,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>3.5527313314558078</v>
+        <v>3.5553084779461672</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>439</v>
@@ -20412,7 +20412,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>4.4612851476900524</v>
+        <v>4.4645617627591028</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>440</v>
@@ -20428,7 +20428,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>5.4715667789839957</v>
+        <v>5.4756250697632325</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>442</v>
@@ -20444,7 +20444,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>6.156008399483123</v>
+        <v>6.1605980250885715</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>441</v>
@@ -20465,22 +20465,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20670,10 +20670,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20689,22 +20689,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20738,7 +20738,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>8.7423732285332623E-2</v>
+        <v>8.884068624954182E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20748,7 +20748,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>5.9395248380129599E-2</v>
+        <v>6.0307017543859656E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>372</v>
@@ -20839,22 +20839,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>478</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20862,13 +20862,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -20889,7 +20889,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-1.1063177352195119</v>
+        <v>-1.1072515257407711</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -20951,7 +20951,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.7741607618044789</v>
+        <v>0.77481419432055476</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -20982,7 +20982,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.29814530999923367</v>
+        <v>0.29839696036654872</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -20995,7 +20995,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>-3.4011663415799351E-2</v>
+        <v>-3.4040371053667626E-2</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21017,33 +21017,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21106,23 +21106,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21140,7 +21140,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>0.86519855574258797</v>
+        <v>0.86592882895853629</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21154,7 +21154,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>7.8301277287882352</v>
+        <v>7.8367367695914547</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21166,13 +21166,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.18 HKD</v>
+        <v>8.19 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21240,7 +21240,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>7.03 HKD</v>
+        <v>7.04 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21284,7 +21284,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>6.04 HKD</v>
+        <v>6.05 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21306,7 +21306,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>5.6 HKD</v>
+        <v>5.61 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21328,7 +21328,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>6.7081007352084114</v>
+        <v>6.7137627260477304</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21336,13 +21336,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21355,22 +21355,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21435,11 +21435,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>3.0533002891253571</v>
+        <v>3.0558774356157166</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>3.5527313314558078</v>
+        <v>3.5553084779461672</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21456,11 +21456,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>3.8820027402826454</v>
+        <v>3.8852793553516958</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>4.4612851476900524</v>
+        <v>4.4645617627591028</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21496,11 +21496,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>4.808100919350867</v>
+        <v>4.8121592101301038</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>5.4715667789839957</v>
+        <v>5.4756250697632325</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21517,11 +21517,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>5.4376052120105438</v>
+        <v>5.4421948376159923</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>6.156008399483123</v>
+        <v>6.1605980250885715</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21539,13 +21539,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21553,13 +21553,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21596,22 +21596,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>387</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21635,15 +21635,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21658,12 +21655,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/1368.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1368.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CC27906-2286-452F-9CE1-E0F17C730755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFF3D0B9-8251-4C28-9F25-484E9BBE66C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,6 +5025,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5034,16 +5043,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>349</v>
       </c>
       <c r="C8" s="47">
-        <v>4.5599999999999996</v>
+        <v>4.53</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>12795.689943359999</v>
+        <v>12711.507772680001</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.19114376894438945</v>
+        <v>0.19361913343073964</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>354</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>353</v>
       </c>
       <c r="E16" s="416">
-        <v>1.14663</v>
+        <v>1.1457459999999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>6.7137627260477304</v>
+        <v>6.7085867178761092</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>346</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>3.5553084779461672</v>
+        <v>3.5529525343086519</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>405</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>4.4645617627591028</v>
+        <v>4.4615663876597855</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>406</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>5.4756250697632325</v>
+        <v>5.4719151121118932</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>407</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>6.1605980250885715</v>
+        <v>6.1564023383923807</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>408</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>8.884068624954182E-2</v>
+        <v>8.9360089413563742E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.0307017543859656E-2</v>
+        <v>6.070640176600442E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>477</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-1.1072515257407711</v>
+        <v>-1.1063978847678724</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.77481419432055476</v>
+        <v>0.77421684753233233</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.29839696036654872</v>
+        <v>0.29816690977222965</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>-3.4040371053667626E-2</v>
+        <v>-3.4014127463310277E-2</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>484</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>482</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>0.86592882895853629</v>
+        <v>0.86526123689762791</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>7.8367367695914547</v>
+        <v>7.8306949990950256</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>490</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.19 HKD</v>
+        <v>8.18 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-2.8172352000014306E-2</v>
+        <v>-2.8144717931147662E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>7.04 HKD</v>
+        <v>7.03 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.4220995039074499E-2</v>
+        <v>2.4251605594504216E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.1461124895888617E-2</v>
+        <v>5.1493361164113217E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>6.05 HKD</v>
+        <v>6.04 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>7.9404693593109255E-2</v>
+        <v>7.9438654318716717E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>5.61 HKD</v>
+        <v>5.6 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.10805571624597797</v>
+        <v>0.10809150572694863</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>6.7137627260477304</v>
+        <v>6.7085867178761092</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>358</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>3.0558774356157166</v>
+        <v>3.0535214919782012</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>3.5553084779461672</v>
+        <v>3.5529525343086519</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6610,11 +6610,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>3.8852793553516958</v>
+        <v>3.8822839802523781</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>4.4645617627591028</v>
+        <v>4.4615663876597855</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>4.8121592101301038</v>
+        <v>4.8084492524787645</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>5.4756250697632325</v>
+        <v>5.4719151121118932</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>5.4421948376159923</v>
+        <v>5.4379991509198016</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>6.1605980250885715</v>
+        <v>6.1564023383923807</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>359</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>437</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,6 +6796,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6812,18 +6824,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -9946,11 +9946,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>4.1690011743553201</v>
+        <v>4.1657870625336075</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>0.86592882895853629</v>
+        <v>0.86526123689762791</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10356,11 +10356,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-3107027.8975200001</v>
+        <v>-3104632.5191839999</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-1.1072515257407711</v>
+        <v>-1.1063978847678724</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10373,11 +10373,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>2174184.6917193206</v>
+        <v>2172508.4934099442</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.77481419432055476</v>
+        <v>0.77421684753233211</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10390,11 +10390,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>837323.46159900003</v>
+        <v>836677.92298579996</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.29839696036654872</v>
+        <v>0.29816690977222965</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10407,11 +10407,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>-95519.744201679481</v>
+        <v>-95446.102788255666</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>-3.404037105366764E-2</v>
+        <v>-3.4014127463310617E-2</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -13994,16 +13994,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.0307017543859656E-2</v>
+        <v>6.070640176600442E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.0307017543859656E-2</v>
+        <v>6.070640176600442E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.5043859649122812E-2</v>
+        <v>5.5408388520971297E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15158,18 +15158,18 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.40511352929791067</v>
+        <v>0.40480120504344375</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.3267986944204086</v>
+        <v>0.32654674737047301</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.3581500029252988</v>
+        <v>0.35787388543091436</v>
       </c>
       <c r="I123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15215,18 +15215,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.884068624954182E-2</v>
+        <v>8.9360089413563742E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.1666380355352763E-2</v>
+        <v>7.2085374695468649E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.8541667308179575E-2</v>
+        <v>7.9000857711018613E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15272,11 +15272,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10719007775831128</v>
+        <v>0.10789994582293586</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10202685480648571</v>
+        <v>0.10270252934162799</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16197,7 +16197,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>-3.4040371053667626E-2</v>
+        <v>-3.4014127463310277E-2</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.14663</v>
+        <v>1.1457459999999999</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16247,7 +16247,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>21990450.410399321</v>
+        <v>21973496.765227996</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16269,7 +16269,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>7.8367367695914547</v>
+        <v>7.8306949990950256</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16392,7 +16392,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>6.7153649112947269</v>
+        <v>6.7101876679105619</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18580,23 +18580,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>7.8367367695914547</v>
+        <v>7.8306949990950256</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>7.8367367695914547</v>
+        <v>7.8306949990950256</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>7.8367367695914547</v>
+        <v>7.8306949990950256</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>7.8367367695914547</v>
+        <v>7.8306949990950256</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>7.8367367695914547</v>
+        <v>7.8306949990950256</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18611,23 +18611,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>5.6579333385576804</v>
+        <v>5.6535713272102663</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>5.7148530756537923</v>
+        <v>5.7104471817570008</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>5.7717728127499068</v>
+        <v>5.7673230363037371</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>5.8286925498460214</v>
+        <v>5.8241988908504734</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>5.9425320240382478</v>
+        <v>5.937950599943945</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18642,23 +18642,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>5.650889455435153</v>
+        <v>5.6465328746038423</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>5.761341489799876</v>
+        <v>5.7568997554330936</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>5.872854964483408</v>
+        <v>5.8683272582585548</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>5.9854298794857526</v>
+        <v>5.9808153830802286</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>6.2137640304468631</v>
+        <v>6.2089734987122007</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18673,23 +18673,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>5.6443217322439834</v>
+        <v>5.6399702148309521</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>5.8051207889024816</v>
+        <v>5.8006453026711862</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>5.9689890388593287</v>
+        <v>5.9643872176002022</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>6.1359561727528131</v>
+        <v>6.1312256273661454</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>6.4793058549028473</v>
+        <v>6.4743106024013999</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18704,23 +18704,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>5.638197981016785</v>
+        <v>5.6338511847396777</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>5.8463488467986391</v>
+        <v>5.8418415755947022</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>6.0604172494546074</v>
+        <v>6.0557449411698778</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>6.2805175546316674</v>
+        <v>6.2756755589414324</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>6.7392768718527627</v>
+        <v>6.7340811934257916</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18735,23 +18735,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>5.6324881896627552</v>
+        <v>5.6281457953771854</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>5.8851743372183325</v>
+        <v>5.8806371333128862</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>6.147369953237531</v>
+        <v>6.1426306083410411</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>6.4193503969022716</v>
+        <v>6.4144013673540625</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>6.9937939513841485</v>
+        <v>6.9884020517713488</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18766,23 +18766,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>5.6271643748804436</v>
+        <v>5.6228260850158884</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>5.9217372699212589</v>
+        <v>5.917171877644229</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>6.2300662309611488</v>
+        <v>6.2252631309653603</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>6.5526817046306824</v>
+        <v>6.5476298826594324</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>7.2429715117645275</v>
+        <v>7.2373875074942742</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18798,23 +18798,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>5.6222004450134859</v>
+        <v>5.6178659821149113</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>5.9561694955902178</v>
+        <v>5.9515775576205998</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>6.3087144391458496</v>
+        <v>6.3038507049297499</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>6.6807294873442151</v>
+        <v>6.6755789463093453</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>7.4869215708781836</v>
+        <v>7.4811494921181145</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18829,23 +18829,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>5.6175720721771603</v>
+        <v>5.6132411775452349</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>5.9885951813017764</v>
+        <v>5.9839782445913547</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>6.3835127350417888</v>
+        <v>6.3785913347140646</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>6.8037031154980028</v>
+        <v>6.7984577673437592</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>7.7257537965838612</v>
+        <v>7.7197975889526456</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18861,23 +18861,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>5.6132565730290729</v>
+        <v>5.6089290054522971</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>6.0191312582888852</v>
+        <v>6.0144907796407354</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>6.4546495758938685</v>
+        <v>6.449673332271173</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>6.9218036628158623</v>
+        <v>6.9164672644677205</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>7.9595755560159933</v>
+        <v>7.9534390823570806</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18893,23 +18893,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>5.6092327975996206</v>
+        <v>5.6049083321721689</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>6.0478878436100789</v>
+        <v>6.0432251949319946</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>6.5223041937671775</v>
+        <v>6.5172757914863277</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>7.0352242350651792</v>
+        <v>7.0298003945727814</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>8.1884919638516482</v>
+        <v>8.1821790059698163</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18925,23 +18925,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>5.5928443747337147</v>
+        <v>5.5885325440409321</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>6.1684036382307088</v>
+        <v>6.1636480773120192</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>6.8140263791287579</v>
+        <v>6.8087730722039863</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>7.538367165911966</v>
+        <v>7.5325554249190851</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>9.2630209422840366</v>
+        <v>9.2558795710370081</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -18957,23 +18957,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>5.5812952078436187</v>
+        <v>5.5769922810374695</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>6.2576651695879972</v>
+        <v>6.2528407920556495</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>7.0410044041603435</v>
+        <v>7.0355761074183443</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>7.9494137036512909</v>
+        <v>7.9432850643221018</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>10.229468122610591</v>
+        <v>10.221581664188616</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -18989,23 +18989,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>5.5731563370720609</v>
+        <v>5.5688596849680927</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>6.323777839759817</v>
+        <v>6.3189024923414276</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>7.2176074409961686</v>
+        <v>7.2120429912801827</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>8.2852213754457278</v>
+        <v>8.278833843551487</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>11.098704942750864</v>
+        <v>11.090148341956018</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19021,23 +19021,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>5.5674207530194195</v>
+        <v>5.5631285227919962</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>6.3727450162218977</v>
+        <v>6.3678319173196005</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>7.355015600289545</v>
+        <v>7.349345215081887</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>8.5595620694610446</v>
+        <v>8.5529630332685453</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>11.880509333997857</v>
+        <v>11.87134999728832</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19084,7 +19084,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>8.1884919638516482</v>
+        <v>8.1821790059698163</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19112,7 +19112,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>7.0352242350651792</v>
+        <v>7.0298003945727814</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19140,7 +19140,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>6.5223041937671775</v>
+        <v>6.5172757914863277</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19168,7 +19168,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>6.0478878436100789</v>
+        <v>6.0432251949319946</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19196,7 +19196,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>5.6092327975996206</v>
+        <v>5.6049083321721689</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19556,7 +19556,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>7.0352242350651792</v>
+        <v>7.0298003945727814</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19580,7 +19580,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>6.5223041937671775</v>
+        <v>6.5172757914863277</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19603,7 +19603,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>6.0478878436100789</v>
+        <v>6.0432251949319946</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19619,7 +19619,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>6.5062841144875039</v>
+        <v>6.5012680629650355</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19666,7 +19666,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>8.1884919638516482</v>
+        <v>8.1821790059698163</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19689,7 +19689,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>5.6092327975996206</v>
+        <v>5.6049083321721689</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19734,7 +19734,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.5599999999999996</v>
+        <v>4.53</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.19114376894438945</v>
+        <v>0.19361913343073964</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>7.8367367695914547</v>
+        <v>7.8306949990950256</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19765,7 +19765,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>-1.3315966047741299E-2</v>
+        <v>-1.3287507823216489E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19774,7 +19774,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>6.7137627260477304</v>
+        <v>6.7085867178761092</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>6.7153649112947269</v>
+        <v>6.7101876679105619</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19944,7 +19944,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>-5.0702374276051579E-3</v>
+        <v>-5.0702374276052065E-3</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20022,11 +20022,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>3.0558774356157166</v>
+        <v>3.0535214919782012</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>3.5553084779461672</v>
+        <v>3.5529525343086519</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20034,7 +20034,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.47044472332147602</v>
+        <v>0.47038732840089281</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20047,11 +20047,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>3.8852793553516958</v>
+        <v>3.8822839802523781</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>4.4645617627591028</v>
+        <v>4.4615663876597855</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.33501347233531009</v>
+        <v>0.3349469008470557</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20093,11 +20093,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>4.8121592101301038</v>
+        <v>4.8084492524787645</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>5.4756250697632325</v>
+        <v>5.4719151121118932</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20105,7 +20105,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.18441784537318118</v>
+        <v>0.18434159947115325</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20118,11 +20118,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>5.4421948376159923</v>
+        <v>5.4379991509198016</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>6.1605980250885715</v>
+        <v>6.1564023383923807</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>8.2392649774919446E-2</v>
+        <v>8.2310090441604422E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.5599999999999996</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20259,14 +20259,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>12795.689943359999</v>
+        <v>12711.507772680001</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.19114376894438945</v>
+        <v>0.19361913343073964</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20274,13 +20274,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20318,7 +20318,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.14663</v>
+        <v>1.1457459999999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20344,7 +20344,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>6.7137627260477304</v>
+        <v>6.7085867178761092</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>361</v>
@@ -20396,7 +20396,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>3.5553084779461672</v>
+        <v>3.5529525343086519</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>439</v>
@@ -20412,7 +20412,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>4.4645617627591028</v>
+        <v>4.4615663876597855</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>440</v>
@@ -20428,7 +20428,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>5.4756250697632325</v>
+        <v>5.4719151121118932</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>442</v>
@@ -20444,7 +20444,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>6.1605980250885715</v>
+        <v>6.1564023383923807</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>441</v>
@@ -20465,22 +20465,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20670,10 +20670,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20689,22 +20689,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20738,7 +20738,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>8.884068624954182E-2</v>
+        <v>8.9360089413563742E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20748,7 +20748,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>6.0307017543859656E-2</v>
+        <v>6.070640176600442E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>372</v>
@@ -20839,22 +20839,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>478</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20862,13 +20862,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -20889,7 +20889,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-1.1072515257407711</v>
+        <v>-1.1063978847678724</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -20951,7 +20951,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.77481419432055476</v>
+        <v>0.77421684753233233</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -20982,7 +20982,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.29839696036654872</v>
+        <v>0.29816690977222965</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -20995,7 +20995,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>-3.4040371053667626E-2</v>
+        <v>-3.4014127463310277E-2</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21017,33 +21017,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21106,23 +21106,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21140,7 +21140,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>0.86592882895853629</v>
+        <v>0.86526123689762791</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21154,7 +21154,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>7.8367367695914547</v>
+        <v>7.8306949990950256</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21166,13 +21166,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.19 HKD</v>
+        <v>8.18 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21240,7 +21240,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>7.04 HKD</v>
+        <v>7.03 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21284,7 +21284,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>6.05 HKD</v>
+        <v>6.04 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21306,7 +21306,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>5.61 HKD</v>
+        <v>5.6 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21328,7 +21328,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>6.7137627260477304</v>
+        <v>6.7085867178761092</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21336,13 +21336,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21355,22 +21355,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21435,11 +21435,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>3.0558774356157166</v>
+        <v>3.0535214919782012</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>3.5553084779461672</v>
+        <v>3.5529525343086519</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21456,11 +21456,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>3.8852793553516958</v>
+        <v>3.8822839802523781</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>4.4645617627591028</v>
+        <v>4.4615663876597855</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21496,11 +21496,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>4.8121592101301038</v>
+        <v>4.8084492524787645</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>5.4756250697632325</v>
+        <v>5.4719151121118932</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21517,11 +21517,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>5.4421948376159923</v>
+        <v>5.4379991509198016</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>6.1605980250885715</v>
+        <v>6.1564023383923807</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21539,13 +21539,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21553,13 +21553,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21596,22 +21596,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>387</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21635,12 +21635,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21655,15 +21658,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/1368.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1368.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFF3D0B9-8251-4C28-9F25-484E9BBE66C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79F4F537-84A8-4502-96F9-E0CDA4B093E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,25 +5025,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>349</v>
       </c>
       <c r="C8" s="47">
-        <v>4.53</v>
+        <v>4.57</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>12711.507772680001</v>
+        <v>12823.750666919999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.19361913343073964</v>
+        <v>0.19011280642061121</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>354</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>353</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1457459999999999</v>
+        <v>1.146258</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>6.7085867178761092</v>
+        <v>6.7115845868623873</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>346</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>3.5529525343086519</v>
+        <v>3.5543170627502896</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>405</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>4.4615663876597855</v>
+        <v>4.463301265545363</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>406</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>5.4719151121118932</v>
+        <v>5.4740638658647054</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>407</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>6.1564023383923807</v>
+        <v>6.1588324193747894</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>408</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>8.9360089413563742E-2</v>
+        <v>8.8617527074242627E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.070640176600442E-2</v>
+        <v>6.0175054704595186E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>477</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-1.1063978847678724</v>
+        <v>-1.1068923012589629</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.77421684753233233</v>
+        <v>0.77456282214270533</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.29816690977222965</v>
+        <v>0.29830015174540997</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>-3.4014127463310277E-2</v>
+        <v>-3.4029327370847566E-2</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>482</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>0.86526123689762791</v>
+        <v>0.86564789655281471</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>7.8306949990950256</v>
+        <v>7.8341943050839076</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>490</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.18 HKD</v>
+        <v>8.19 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-2.8144717931147662E-2</v>
+        <v>-2.816072836967181E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.4251605594504216E-2</v>
+        <v>2.4233870652568525E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.1493361164113217E-2</v>
+        <v>5.1474684323504237E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>6.04 HKD</v>
+        <v>6.05 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>7.9438654318716717E-2</v>
+        <v>7.9418978368831772E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>5.6 HKD</v>
+        <v>5.61 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.10809150572694863</v>
+        <v>0.10807077023962144</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>356</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>6.7085867178761092</v>
+        <v>6.7115845868623873</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>358</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>3.0535214919782012</v>
+        <v>3.0548860204198389</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>3.5529525343086519</v>
+        <v>3.5543170627502896</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6610,11 +6610,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>3.8822839802523781</v>
+        <v>3.8840188581379556</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>4.4615663876597855</v>
+        <v>4.463301265545363</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>4.8084492524787645</v>
+        <v>4.8105980062315767</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>5.4719151121118932</v>
+        <v>5.4740638658647054</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>5.4379991509198016</v>
+        <v>5.4404292319022103</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>6.1564023383923807</v>
+        <v>6.1588324193747894</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>437</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,18 +6796,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6824,6 +6812,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -9946,11 +9946,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>4.1657870625336075</v>
+        <v>4.167648629561568</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>0.86526123689762791</v>
+        <v>0.86564789655281471</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10356,11 +10356,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-3104632.5191839999</v>
+        <v>-3106019.8876319998</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-1.1063978847678724</v>
+        <v>-1.1068923012589629</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10373,11 +10373,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>2172508.4934099442</v>
+        <v>2173479.3231999902</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.77421684753233211</v>
+        <v>0.77456282214270533</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10390,11 +10390,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>836677.92298579996</v>
+        <v>837051.80960340006</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.29816690977222965</v>
+        <v>0.29830015174540997</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10407,11 +10407,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>-95446.102788255666</v>
+        <v>-95488.754828609526</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>-3.4014127463310617E-2</v>
+        <v>-3.4029327370847573E-2</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -13994,16 +13994,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.070640176600442E-2</v>
+        <v>6.0175054704595186E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.070640176600442E-2</v>
+        <v>6.0175054704595186E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.5408388520971297E-2</v>
+        <v>5.4923413566739604E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15158,18 +15158,18 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.40480120504344375</v>
+        <v>0.40498209872928886</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.32654674737047301</v>
+        <v>0.32669267145369363</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.35787388543091436</v>
+        <v>0.35803380868558043</v>
       </c>
       <c r="I123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15215,18 +15215,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.9360089413563742E-2</v>
+        <v>8.8617527074242627E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.2085374695468649E-2</v>
+        <v>7.148636136842311E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.9000857711018613E-2</v>
+        <v>7.8344378268179526E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15272,11 +15272,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10789994582293586</v>
+        <v>0.10695552616584232</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10270252934162799</v>
+        <v>0.10180360129487413</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16197,7 +16197,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>-3.4014127463310277E-2</v>
+        <v>-3.4029327370847566E-2</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1457459999999999</v>
+        <v>1.146258</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16247,7 +16247,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>21973496.765227996</v>
+        <v>21983316.071028583</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16269,7 +16269,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>7.8306949990950256</v>
+        <v>7.8341943050839076</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16392,7 +16392,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>6.7101876679105619</v>
+        <v>6.7131862523140606</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18580,23 +18580,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>7.8306949990950256</v>
+        <v>7.8341943050839076</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>7.8306949990950256</v>
+        <v>7.8341943050839076</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>7.8306949990950256</v>
+        <v>7.8341943050839076</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>7.8306949990950256</v>
+        <v>7.8341943050839076</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>7.8306949990950256</v>
+        <v>7.8341943050839076</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18611,23 +18611,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>5.6535713272102663</v>
+        <v>5.656097741022343</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>5.7104471817570008</v>
+        <v>5.7129990117062741</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>5.7673230363037371</v>
+        <v>5.769900282390207</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>5.8241988908504734</v>
+        <v>5.8268015530741391</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>5.937950599943945</v>
+        <v>5.9406040944420022</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18642,23 +18642,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>5.6465328746038423</v>
+        <v>5.6490561431396236</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>5.7568997554330936</v>
+        <v>5.7594723436636279</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>5.8683272582585548</v>
+        <v>5.8709496401444428</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>5.9808153830802286</v>
+        <v>5.9834880325820707</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>6.2089734987122007</v>
+        <v>6.2117481053277519</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18673,23 +18673,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>5.6399702148309521</v>
+        <v>5.6424905507081826</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>5.8006453026711862</v>
+        <v>5.803237439492932</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>5.9643872176002022</v>
+        <v>5.9670525258407832</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>6.1312256273661454</v>
+        <v>6.133965490757519</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>6.4743106024013999</v>
+        <v>6.4772037803207896</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18704,23 +18704,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>5.6338511847396777</v>
+        <v>5.6363687862033416</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>5.8418415755947022</v>
+        <v>5.8444521218123668</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>6.0557449411698778</v>
+        <v>6.0584510744750606</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>6.2756755589414324</v>
+        <v>6.2784799727348721</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>6.7340811934257916</v>
+        <v>6.7370904551391506</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18735,23 +18735,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>5.6281457953771854</v>
+        <v>5.6306608472710904</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>5.8806371333128862</v>
+        <v>5.8832650161178499</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>6.1426306083410411</v>
+        <v>6.1453755682810893</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>6.4144013673540625</v>
+        <v>6.4172677736082289</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>6.9884020517713488</v>
+        <v>6.9915249619543278</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18766,23 +18766,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>5.6228260850158884</v>
+        <v>5.6253387596885718</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>5.917171877644229</v>
+        <v>5.9198160867458576</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>6.2252631309653603</v>
+        <v>6.2280450169357717</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>6.5476298826594324</v>
+        <v>6.5505558247966267</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>7.2373875074942742</v>
+        <v>7.2406216819132441</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18798,23 +18798,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>5.6178659821149113</v>
+        <v>5.6203764402643115</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>5.9515775576205998</v>
+        <v>5.9542371416030031</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>6.3038507049297499</v>
+        <v>6.3066677093626042</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>6.6755789463093453</v>
+        <v>6.678562065098772</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>7.4811494921181145</v>
+        <v>7.4844925965583355</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18829,23 +18829,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>5.6132411775452349</v>
+        <v>5.61574956900626</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>5.9839782445913547</v>
+        <v>5.9866523074824585</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>6.3785913347140646</v>
+        <v>6.3814417385237867</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>6.7984577673437592</v>
+        <v>6.8014957970439545</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>7.7197975889526456</v>
+        <v>7.7232473381689157</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18861,23 +18861,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>5.6089290054522971</v>
+        <v>5.6114354699311537</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>6.0144907796407354</v>
+        <v>6.0171784776812931</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>6.449673332271173</v>
+        <v>6.452555500523232</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>6.9164672644677205</v>
+        <v>6.9195580291218475</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>7.9534390823570806</v>
+        <v>7.9569932390464055</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18893,23 +18893,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>5.6049083321721689</v>
+        <v>5.6074129999310545</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>6.0432251949319946</v>
+        <v>6.0459257335328767</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>6.5172757914863277</v>
+        <v>6.5201881692779509</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>7.0298003945727814</v>
+        <v>7.032941804450731</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>8.1821790059698163</v>
+        <v>8.1858353797656278</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18925,23 +18925,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>5.5885325440409321</v>
+        <v>5.5910298939444445</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>6.1636480773120192</v>
+        <v>6.1664024293373236</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>6.8087730722039863</v>
+        <v>6.8118157115088316</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>7.5325554249190851</v>
+        <v>7.5359215011502556</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>9.2558795710370081</v>
+        <v>9.260015749858816</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -18957,23 +18957,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>5.5769922810374695</v>
+        <v>5.579484473938769</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>6.2528407920556495</v>
+        <v>6.2556350016671454</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>7.0355761074183443</v>
+        <v>7.0387200982915381</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>7.9432850643221018</v>
+        <v>7.9468346834810895</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>10.221581664188616</v>
+        <v>10.22614938671356</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -18989,23 +18989,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>5.5688596849680927</v>
+        <v>5.5713482436527437</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>6.3189024923414276</v>
+        <v>6.3217262229728934</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>7.2120429912801827</v>
+        <v>7.2152658399844638</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>8.278833843551487</v>
+        <v>8.2825334095354819</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>11.090148341956018</v>
+        <v>11.095104201239911</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19021,23 +19021,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>5.5631285227919962</v>
+        <v>5.5656145203897802</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>6.3678319173196005</v>
+        <v>6.3706775130639173</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>7.349345215081887</v>
+        <v>7.3526294200890376</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>8.5529630332685453</v>
+        <v>8.5567850994795851</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>11.87134999728832</v>
+        <v>11.876654952486604</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19084,7 +19084,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>8.1821790059698163</v>
+        <v>8.1858353797656278</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19112,7 +19112,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>7.0298003945727814</v>
+        <v>7.032941804450731</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19140,7 +19140,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>6.5172757914863277</v>
+        <v>6.5201881692779509</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19168,7 +19168,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>6.0432251949319946</v>
+        <v>6.0459257335328767</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19196,7 +19196,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>5.6049083321721689</v>
+        <v>5.6074129999310545</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19556,7 +19556,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>7.0298003945727814</v>
+        <v>7.032941804450731</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19580,7 +19580,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>6.5172757914863277</v>
+        <v>6.5201881692779509</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19603,7 +19603,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>6.0432251949319946</v>
+        <v>6.0459257335328767</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19619,7 +19619,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>6.5012680629650355</v>
+        <v>6.5041732873762381</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19666,7 +19666,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>8.1821790059698163</v>
+        <v>8.1858353797656278</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19689,7 +19689,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>5.6049083321721689</v>
+        <v>5.6074129999310545</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19734,7 +19734,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.53</v>
+        <v>4.57</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.19361913343073964</v>
+        <v>0.19011280642061121</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>7.8306949990950256</v>
+        <v>7.8341943050839076</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19765,7 +19765,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>-1.3287507823216489E-2</v>
+        <v>-1.3303995757223155E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19774,7 +19774,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>6.7085867178761092</v>
+        <v>6.7115845868623873</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>6.7101876679105619</v>
+        <v>6.7131862523140606</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19944,7 +19944,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>-5.0702374276052065E-3</v>
+        <v>-5.070237427605157E-3</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20022,11 +20022,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>3.0535214919782012</v>
+        <v>3.0548860204198389</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>3.5529525343086519</v>
+        <v>3.5543170627502896</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20034,7 +20034,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.47038732840089281</v>
+        <v>0.47042058149610466</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20047,11 +20047,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>3.8822839802523781</v>
+        <v>3.8840188581379556</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>4.4615663876597855</v>
+        <v>4.463301265545363</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.3349469008470557</v>
+        <v>0.33498547060226791</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20093,11 +20093,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>4.8084492524787645</v>
+        <v>4.8105980062315767</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>5.4719151121118932</v>
+        <v>5.4740638658647054</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20105,7 +20105,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.18434159947115325</v>
+        <v>0.18438577432519754</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20118,11 +20118,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>5.4379991509198016</v>
+        <v>5.4404292319022103</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>6.1564023383923807</v>
+        <v>6.1588324193747894</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>8.2310090441604422E-2</v>
+        <v>8.2357923130341626E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.53</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20259,14 +20259,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>12711.507772680001</v>
+        <v>12823.750666919999</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.19361913343073964</v>
+        <v>0.19011280642061121</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20274,13 +20274,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20318,7 +20318,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1457459999999999</v>
+        <v>1.146258</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20344,7 +20344,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>6.7085867178761092</v>
+        <v>6.7115845868623873</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>361</v>
@@ -20396,7 +20396,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>3.5529525343086519</v>
+        <v>3.5543170627502896</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>439</v>
@@ -20412,7 +20412,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>4.4615663876597855</v>
+        <v>4.463301265545363</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>440</v>
@@ -20428,7 +20428,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>5.4719151121118932</v>
+        <v>5.4740638658647054</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>442</v>
@@ -20444,7 +20444,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>6.1564023383923807</v>
+        <v>6.1588324193747894</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>441</v>
@@ -20465,22 +20465,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20670,10 +20670,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20689,22 +20689,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20738,7 +20738,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>8.9360089413563742E-2</v>
+        <v>8.8617527074242627E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20748,7 +20748,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>6.070640176600442E-2</v>
+        <v>6.0175054704595186E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>372</v>
@@ -20839,22 +20839,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>478</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20862,13 +20862,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -20889,7 +20889,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-1.1063978847678724</v>
+        <v>-1.1068923012589629</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -20951,7 +20951,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.77421684753233233</v>
+        <v>0.77456282214270533</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -20982,7 +20982,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.29816690977222965</v>
+        <v>0.29830015174540997</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -20995,7 +20995,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>-3.4014127463310277E-2</v>
+        <v>-3.4029327370847566E-2</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21017,33 +21017,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21106,23 +21106,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21140,7 +21140,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>0.86526123689762791</v>
+        <v>0.86564789655281471</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21154,7 +21154,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>7.8306949990950256</v>
+        <v>7.8341943050839076</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21166,13 +21166,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.18 HKD</v>
+        <v>8.19 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21284,7 +21284,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>6.04 HKD</v>
+        <v>6.05 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21306,7 +21306,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>5.6 HKD</v>
+        <v>5.61 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21328,7 +21328,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>6.7085867178761092</v>
+        <v>6.7115845868623873</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21336,13 +21336,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21355,22 +21355,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21435,11 +21435,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>3.0535214919782012</v>
+        <v>3.0548860204198389</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>3.5529525343086519</v>
+        <v>3.5543170627502896</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21456,11 +21456,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>3.8822839802523781</v>
+        <v>3.8840188581379556</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>4.4615663876597855</v>
+        <v>4.463301265545363</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21496,11 +21496,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>4.8084492524787645</v>
+        <v>4.8105980062315767</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>5.4719151121118932</v>
+        <v>5.4740638658647054</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21517,11 +21517,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>5.4379991509198016</v>
+        <v>5.4404292319022103</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>6.1564023383923807</v>
+        <v>6.1588324193747894</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21539,13 +21539,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21553,13 +21553,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21596,22 +21596,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>387</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21635,15 +21635,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21658,12 +21655,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/1368.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1368.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79F4F537-84A8-4502-96F9-E0CDA4B093E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17A3E67-9093-4059-8C0D-E814D40157B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,6 +5025,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5034,16 +5043,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>349</v>
       </c>
       <c r="C8" s="47">
-        <v>4.57</v>
+        <v>4.49</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>12823.750666919999</v>
+        <v>12599.264878440001</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.19011280642061121</v>
+        <v>0.19723184159698909</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>354</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>353</v>
       </c>
       <c r="E16" s="416">
-        <v>1.146258</v>
+        <v>1.1454299999999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>6.7115845868623873</v>
+        <v>6.7067364706111396</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>346</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>3.5543170627502896</v>
+        <v>3.5521103644110781</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>405</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>4.463301265545363</v>
+        <v>4.4604956427147799</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>406</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>5.4740638658647054</v>
+        <v>5.4705889281550792</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>407</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>6.1588324193747894</v>
+        <v>6.1549025227860499</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>408</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>8.8617527074242627E-2</v>
+        <v>9.0131305060514755E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.0175054704595186E-2</v>
+        <v>6.1247216035634745E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>477</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-1.1068923012589629</v>
+        <v>-1.1060927370897773</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.77456282214270533</v>
+        <v>0.77400331632749264</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.29830015174540997</v>
+        <v>0.29808467449190751</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>-3.4029327370847566E-2</v>
+        <v>-3.4004746270377105E-2</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>484</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>482</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>0.86564789655281471</v>
+        <v>0.86502259539169235</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>7.8341943050839076</v>
+        <v>7.8285352711800131</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>490</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.19 HKD</v>
+        <v>8.18 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-2.816072836967181E-2</v>
+        <v>-2.8134829356997799E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.4233870652568525E-2</v>
+        <v>2.4262559288265439E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.1474684323504237E-2</v>
+        <v>5.1504896611395477E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>6.05 HKD</v>
+        <v>6.04 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>7.9418978368831772E-2</v>
+        <v>7.9450806855547923E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>5.61 HKD</v>
+        <v>5.6 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.10807077023962144</v>
+        <v>0.10810431267673655</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>6.7115845868623873</v>
+        <v>6.7067364706111396</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>358</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>3.0548860204198389</v>
+        <v>3.0526793220806274</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>3.5543170627502896</v>
+        <v>3.5521103644110781</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6610,11 +6610,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>3.8840188581379556</v>
+        <v>3.8812132353073725</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>4.463301265545363</v>
+        <v>4.4604956427147799</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>4.8105980062315767</v>
+        <v>4.8071230685219506</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>5.4740638658647054</v>
+        <v>5.4705889281550792</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>5.4404292319022103</v>
+        <v>5.4364993353134707</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>6.1588324193747894</v>
+        <v>6.1549025227860499</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>359</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>437</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,6 +6796,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6812,18 +6824,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -9946,11 +9946,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>4.167648629561568</v>
+        <v>4.1646381266335384</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>0.86564789655281471</v>
+        <v>0.86502259539169235</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10356,11 +10356,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-3106019.8876319998</v>
+        <v>-3103776.2527199998</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-1.1068923012589629</v>
+        <v>-1.1060927370897773</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10373,11 +10373,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>2173479.3231999902</v>
+        <v>2171909.3093989007</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.77456282214270533</v>
+        <v>0.77400331632749264</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10390,11 +10390,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>837051.80960340006</v>
+        <v>836447.16483899998</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.29830015174540997</v>
+        <v>0.29808467449190751</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10407,11 +10407,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>-95488.754828609526</v>
+        <v>-95419.778482099064</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>-3.4029327370847573E-2</v>
+        <v>-3.400474627037714E-2</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -13994,16 +13994,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.0175054704595186E-2</v>
+        <v>6.1247216035634745E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.0175054704595186E-2</v>
+        <v>6.1247216035634745E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.4923413566739604E-2</v>
+        <v>5.5902004454342985E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15158,18 +15158,18 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.40498209872928886</v>
+        <v>0.40468955972171128</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.32669267145369363</v>
+        <v>0.32645668485036028</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.35803380868558043</v>
+        <v>0.35777518279717513</v>
       </c>
       <c r="I123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15215,18 +15215,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.8617527074242627E-2</v>
+        <v>9.0131305060514755E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.148636136842311E-2</v>
+        <v>7.2707502193844156E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.8344378268179526E-2</v>
+        <v>7.9682668774426535E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15272,11 +15272,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10695552616584232</v>
+        <v>0.10886119255632504</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10180360129487413</v>
+        <v>0.10361747392373603</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16197,7 +16197,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>-3.4029327370847566E-2</v>
+        <v>-3.4004746270377105E-2</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.146258</v>
+        <v>1.1454299999999999</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16247,7 +16247,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>21983316.071028583</v>
+        <v>21967436.412429199</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16269,7 +16269,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>7.8341943050839076</v>
+        <v>7.8285352711800131</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16392,7 +16392,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>6.7131862523140606</v>
+        <v>6.7083369790990286</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18580,23 +18580,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>7.8341943050839076</v>
+        <v>7.8285352711800131</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>7.8341943050839076</v>
+        <v>7.8285352711800131</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>7.8341943050839076</v>
+        <v>7.8285352711800131</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>7.8341943050839076</v>
+        <v>7.8285352711800131</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>7.8341943050839076</v>
+        <v>7.8285352711800131</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18611,23 +18611,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>5.656097741022343</v>
+        <v>5.6520120561856251</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>5.7129990117062741</v>
+        <v>5.7088722242101841</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>5.769900282390207</v>
+        <v>5.765732392234745</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>5.8268015530741391</v>
+        <v>5.8225925602593058</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>5.9406040944420022</v>
+        <v>5.9363128963084248</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18642,23 +18642,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>5.6490561431396236</v>
+        <v>5.6449755448044154</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>5.7594723436636279</v>
+        <v>5.7553119861345605</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>5.8709496401444428</v>
+        <v>5.8667087569383582</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>5.9834880325820707</v>
+        <v>5.9791658572158104</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>6.2117481053277519</v>
+        <v>6.2072610461916664</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18673,23 +18673,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>5.6424905507081826</v>
+        <v>5.6384146950317238</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>5.803237439492932</v>
+        <v>5.7990454682265149</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>5.9670525258407832</v>
+        <v>5.96274222267047</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>6.133965490757519</v>
+        <v>6.1295346179292833</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>6.4772037803207896</v>
+        <v>6.4725249691542759</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18704,23 +18704,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>5.6363687862033416</v>
+        <v>5.6322973525863231</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>5.8444521218123668</v>
+        <v>5.8402303791009871</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>6.0584510744750606</v>
+        <v>6.054074749520586</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>6.2784799727348721</v>
+        <v>6.2739447098032937</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>6.7370904551391506</v>
+        <v>6.7322239147120779</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18735,23 +18735,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>5.6306608472710904</v>
+        <v>5.6265935367864168</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>5.8832650161178499</v>
+        <v>5.8790152368941975</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>6.1453755682810893</v>
+        <v>6.1409364533780426</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>6.4172677736082289</v>
+        <v>6.4126322572440699</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>6.9915249619543278</v>
+        <v>6.9864746306427916</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18766,23 +18766,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>5.6253387596885718</v>
+        <v>5.6212752936163417</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>5.9198160867458576</v>
+        <v>5.915539904839318</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>6.2280450169357717</v>
+        <v>6.2235461857179981</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>6.5505558247966267</v>
+        <v>6.5458240277466331</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>7.2406216819132441</v>
+        <v>7.2353914154700663</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18798,23 +18798,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>5.6203764402643115</v>
+        <v>5.6163165587258286</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>5.9542371416030031</v>
+        <v>5.9499360956314611</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>6.3066677093626042</v>
+        <v>6.3021120850063488</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>6.678562065098772</v>
+        <v>6.6737378026814955</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>7.4844925965583355</v>
+        <v>7.4790861698464166</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18829,23 +18829,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>5.61574956900626</v>
+        <v>5.6116930296903833</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>5.9866523074824585</v>
+        <v>5.982327846400751</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>6.3814417385237867</v>
+        <v>6.3768321011127522</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>6.8014957970439545</v>
+        <v>6.7965827333881697</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>7.7232473381689157</v>
+        <v>7.7176684468582293</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18861,23 +18861,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>5.6114354699311537</v>
+        <v>5.6073820469067535</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>6.0171784776812931</v>
+        <v>6.0128319660063294</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>6.452555500523232</v>
+        <v>6.4478944940531067</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>6.9195580291218475</v>
+        <v>6.9145596831577514</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>7.9569932390464055</v>
+        <v>7.9512455012753884</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18893,23 +18893,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>5.6074129999310545</v>
+        <v>5.6033624825397315</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>6.0459257335328767</v>
+        <v>6.0415584562642639</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>6.5201881692779509</v>
+        <v>6.5154783083180607</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>7.032941804450731</v>
+        <v>7.0278615556637343</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>8.1858353797656278</v>
+        <v>8.1799223377677137</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18925,23 +18925,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>5.5910298939444445</v>
+        <v>5.5869912108973585</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>6.1664024293373236</v>
+        <v>6.1619481256714028</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>6.8118157115088316</v>
+        <v>6.8068951932580282</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>7.5359215011502556</v>
+        <v>7.5304779247451599</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>9.260015749858816</v>
+        <v>9.2533267731704232</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -18957,23 +18957,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>5.579484473938769</v>
+        <v>5.5754541307311998</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>6.2556350016671454</v>
+        <v>6.2511162408110543</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>7.0387200982915381</v>
+        <v>7.0336356755512952</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>7.9468346834810895</v>
+        <v>7.9410942837474146</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>10.22614938671356</v>
+        <v>10.218762522942752</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -18989,23 +18989,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>5.5713482436527437</v>
+        <v>5.5673237776549103</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>6.3217262229728934</v>
+        <v>6.3171597210923203</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>7.2152658399844638</v>
+        <v>7.2100538893455086</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>8.2825334095354819</v>
+        <v>8.2765505176707386</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>11.095104201239911</v>
+        <v>11.087089647554242</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19021,23 +19021,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>5.5656145203897802</v>
+        <v>5.5615941961496151</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>6.3706775130639173</v>
+        <v>6.3660756511961551</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>7.3526294200890376</v>
+        <v>7.3473182448040371</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>8.5567850994795851</v>
+        <v>8.5506041017789212</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>11.876654952486604</v>
+        <v>11.86807584525188</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19084,7 +19084,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>8.1858353797656278</v>
+        <v>8.1799223377677137</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19112,7 +19112,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>7.032941804450731</v>
+        <v>7.0278615556637343</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19140,7 +19140,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>6.5201881692779509</v>
+        <v>6.5154783083180607</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19168,7 +19168,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>6.0459257335328767</v>
+        <v>6.0415584562642639</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19196,7 +19196,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>5.6074129999310545</v>
+        <v>5.6033624825397315</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19556,7 +19556,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>7.032941804450731</v>
+        <v>7.0278615556637343</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19580,7 +19580,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>6.5201881692779509</v>
+        <v>6.5154783083180607</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19603,7 +19603,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>6.0459257335328767</v>
+        <v>6.0415584562642639</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19619,7 +19619,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>6.5041732873762381</v>
+        <v>6.4994749947737462</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19666,7 +19666,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>8.1858353797656278</v>
+        <v>8.1799223377677137</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19689,7 +19689,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>5.6074129999310545</v>
+        <v>5.6033624825397315</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19734,7 +19734,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.57</v>
+        <v>4.49</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.19011280642061121</v>
+        <v>0.19723184159698909</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>7.8341943050839076</v>
+        <v>7.8285352711800131</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19765,7 +19765,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>-1.3303995757223155E-2</v>
+        <v>-1.3277324329662294E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19774,7 +19774,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>6.7115845868623873</v>
+        <v>6.7067364706111396</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>6.7131862523140606</v>
+        <v>6.7083369790990286</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19944,7 +19944,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>-5.070237427605157E-3</v>
+        <v>-5.0702374276051605E-3</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20022,11 +20022,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>3.0548860204198389</v>
+        <v>3.0526793220806274</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>3.5543170627502896</v>
+        <v>3.5521103644110781</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20034,7 +20034,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.47042058149610466</v>
+        <v>0.4703667901703914</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20047,11 +20047,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>3.8840188581379556</v>
+        <v>3.8812132353073725</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>4.463301265545363</v>
+        <v>4.4604956427147799</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.33498547060226791</v>
+        <v>0.3349230788684433</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20093,11 +20093,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>4.8105980062315767</v>
+        <v>4.8071230685219506</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>5.4740638658647054</v>
+        <v>5.4705889281550792</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20105,7 +20105,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.18438577432519754</v>
+        <v>0.18431431559490197</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20118,11 +20118,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>5.4404292319022103</v>
+        <v>5.4364993353134707</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>6.1588324193747894</v>
+        <v>6.1549025227860499</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>8.2357923130341626E-2</v>
+        <v>8.2280547363568157E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.57</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20259,14 +20259,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>12823.750666919999</v>
+        <v>12599.264878440001</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.19011280642061121</v>
+        <v>0.19723184159698909</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20274,13 +20274,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20318,7 +20318,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.146258</v>
+        <v>1.1454299999999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20344,7 +20344,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>6.7115845868623873</v>
+        <v>6.7067364706111396</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>361</v>
@@ -20396,7 +20396,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>3.5543170627502896</v>
+        <v>3.5521103644110781</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>439</v>
@@ -20412,7 +20412,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>4.463301265545363</v>
+        <v>4.4604956427147799</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>440</v>
@@ -20428,7 +20428,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>5.4740638658647054</v>
+        <v>5.4705889281550792</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>442</v>
@@ -20444,7 +20444,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>6.1588324193747894</v>
+        <v>6.1549025227860499</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>441</v>
@@ -20465,22 +20465,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20670,10 +20670,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20689,22 +20689,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20738,7 +20738,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>8.8617527074242627E-2</v>
+        <v>9.0131305060514755E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20748,7 +20748,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>6.0175054704595186E-2</v>
+        <v>6.1247216035634745E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>372</v>
@@ -20839,22 +20839,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>478</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20862,13 +20862,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -20889,7 +20889,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-1.1068923012589629</v>
+        <v>-1.1060927370897773</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -20951,7 +20951,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.77456282214270533</v>
+        <v>0.77400331632749264</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -20982,7 +20982,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.29830015174540997</v>
+        <v>0.29808467449190751</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -20995,7 +20995,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>-3.4029327370847566E-2</v>
+        <v>-3.4004746270377105E-2</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21017,33 +21017,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21106,23 +21106,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21140,7 +21140,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>0.86564789655281471</v>
+        <v>0.86502259539169235</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21154,7 +21154,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>7.8341943050839076</v>
+        <v>7.8285352711800131</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21166,13 +21166,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.19 HKD</v>
+        <v>8.18 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21284,7 +21284,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>6.05 HKD</v>
+        <v>6.04 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21306,7 +21306,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>5.61 HKD</v>
+        <v>5.6 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21328,7 +21328,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>6.7115845868623873</v>
+        <v>6.7067364706111396</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21336,13 +21336,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21355,22 +21355,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21435,11 +21435,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>3.0548860204198389</v>
+        <v>3.0526793220806274</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>3.5543170627502896</v>
+        <v>3.5521103644110781</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21456,11 +21456,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>3.8840188581379556</v>
+        <v>3.8812132353073725</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>4.463301265545363</v>
+        <v>4.4604956427147799</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21496,11 +21496,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>4.8105980062315767</v>
+        <v>4.8071230685219506</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>5.4740638658647054</v>
+        <v>5.4705889281550792</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21517,11 +21517,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>5.4404292319022103</v>
+        <v>5.4364993353134707</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>6.1588324193747894</v>
+        <v>6.1549025227860499</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21539,13 +21539,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21553,13 +21553,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21596,22 +21596,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>387</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21635,12 +21635,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21655,15 +21658,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/1368.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1368.HK_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17A3E67-9093-4059-8C0D-E814D40157B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBEF23EB-391E-4EE8-8086-D87FE0ECF09E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,25 +5025,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>349</v>
       </c>
       <c r="C8" s="47">
-        <v>4.49</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>12599.264878440001</v>
+        <v>12206.414748599998</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.19723184159698909</v>
+        <v>0.21026957042132716</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>354</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>353</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1454299999999999</v>
+        <v>1.1444179999999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>6.7067364706111396</v>
+        <v>6.7008109951929491</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>346</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>3.5521103644110781</v>
+        <v>3.5494132886631533</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>405</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>4.4604956427147799</v>
+        <v>4.4570665481440672</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>406</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>5.4705889281550792</v>
+        <v>5.4663417820655376</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>407</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>6.1549025227860499</v>
+        <v>6.1500993158442583</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>408</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>9.0131305060514755E-2</v>
+        <v>9.2949887826616825E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.1247216035634745E-2</v>
+        <v>6.3218390804597707E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>477</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-1.1060927370897773</v>
+        <v>-1.105115491994106</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.77400331632749264</v>
+        <v>0.77331947588667704</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.29808467449190751</v>
+        <v>0.29782131340429341</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>-3.4004746270377105E-2</v>
+        <v>-3.3974702703135441E-2</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>482</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>0.86502259539169235</v>
+        <v>0.86425833841698729</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>7.8285352711800131</v>
+        <v>7.8216186741863654</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>490</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.18 HKD</v>
+        <v>8.17 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-2.8134829356997799E-2</v>
+        <v>-2.8103124195484622E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>7.03 HKD</v>
+        <v>7.02 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.4262559288265439E-2</v>
+        <v>2.4297679529935442E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>6.52 HKD</v>
+        <v>6.51 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.1504896611395477E-2</v>
+        <v>5.1541882125891544E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>7.9450806855547923E-2</v>
+        <v>7.9489770943233382E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.10810431267673655</v>
+        <v>0.1081453750105426</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>356</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>6.7067364706111396</v>
+        <v>6.7008109951929491</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>358</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>3.0526793220806274</v>
+        <v>3.0499822463327027</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>3.5521103644110781</v>
+        <v>3.5494132886631533</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6610,11 +6610,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>3.8812132353073725</v>
+        <v>3.8777841407366602</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>4.4604956427147799</v>
+        <v>4.4570665481440672</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>4.8071230685219506</v>
+        <v>4.8028759224324089</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>5.4705889281550792</v>
+        <v>5.4663417820655376</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>5.4364993353134707</v>
+        <v>5.4316961283716791</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>6.1549025227860499</v>
+        <v>6.1500993158442583</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>437</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,18 +6796,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6824,6 +6812,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -9946,11 +9946,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>4.1646381266335384</v>
+        <v>4.1609586230548361</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>0.86502259539169235</v>
+        <v>0.86425833841698729</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10356,11 +10356,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-3103776.2527199998</v>
+        <v>-3101034.0322719999</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-1.1060927370897773</v>
+        <v>-1.105115491994106</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10373,11 +10373,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>2171909.3093989007</v>
+        <v>2169990.4036420132</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.77400331632749264</v>
+        <v>0.77331947588667704</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10390,11 +10390,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>836447.16483899998</v>
+        <v>835708.15457140002</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.29808467449190751</v>
+        <v>0.29782131340429341</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10407,11 +10407,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>-95419.778482099064</v>
+        <v>-95335.474058586638</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>-3.400474627037714E-2</v>
+        <v>-3.3974702703135518E-2</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -13994,16 +13994,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.1247216035634745E-2</v>
+        <v>6.3218390804597707E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.1247216035634745E-2</v>
+        <v>6.3218390804597707E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.5902004454342985E-2</v>
+        <v>5.7701149425287361E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15158,18 +15158,18 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.40468955972171128</v>
+        <v>0.40433201204578312</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.32645668485036028</v>
+        <v>0.32616825677961953</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.35777518279717513</v>
+        <v>0.35745908448912428</v>
       </c>
       <c r="I123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15215,18 +15215,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.0131305060514755E-2</v>
+        <v>9.2949887826616825E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.2707502193844156E-2</v>
+        <v>7.4981208455084949E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>7.9682668774426535E-2</v>
+        <v>8.2174502181407885E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15272,11 +15272,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10886119255632504</v>
+        <v>0.11236477116733322</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10361747392373603</v>
+        <v>0.106952289176454</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16197,7 +16197,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>-3.4004746270377105E-2</v>
+        <v>-3.3974702703135441E-2</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1454299999999999</v>
+        <v>1.1444179999999999</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16247,7 +16247,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>21967436.412429199</v>
+        <v>21948027.94080773</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16269,7 +16269,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>7.8285352711800131</v>
+        <v>7.8216186741863654</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16392,7 +16392,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>6.7083369790990286</v>
+        <v>6.7024100896139895</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18580,23 +18580,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>7.8285352711800131</v>
+        <v>7.8216186741863654</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>7.8285352711800131</v>
+        <v>7.8216186741863654</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>7.8285352711800131</v>
+        <v>7.8216186741863654</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>7.8285352711800131</v>
+        <v>7.8216186741863654</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>7.8285352711800131</v>
+        <v>7.8216186741863654</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18611,23 +18611,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>5.6520120561856251</v>
+        <v>5.6470184413851925</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>5.7088722242101841</v>
+        <v>5.7038283728260746</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>5.765732392234745</v>
+        <v>5.7606383042669584</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>5.8225925602593058</v>
+        <v>5.8174482357078423</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>5.9363128963084248</v>
+        <v>5.9310680985896083</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18642,23 +18642,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>5.6449755448044154</v>
+        <v>5.6399881468391602</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>5.7553119861345605</v>
+        <v>5.7502271047101452</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>5.8667087569383582</v>
+        <v>5.8615254552420337</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>5.9791658572158104</v>
+        <v>5.9738831984348266</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>6.2072610461916664</v>
+        <v>6.2017768628031167</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18673,23 +18673,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>5.6384146950317238</v>
+        <v>5.6334330936493853</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>5.7990454682265149</v>
+        <v>5.7939219477897836</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>5.96274222267047</v>
+        <v>5.9574740743511985</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>6.1295346179292833</v>
+        <v>6.1241191066947733</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>6.4725249691542759</v>
+        <v>6.4668064221729811</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18704,23 +18704,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>5.6322973525863231</v>
+        <v>5.6273211559433003</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>5.8402303791009871</v>
+        <v>5.8350704713426342</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>6.054074749520586</v>
+        <v>6.0487259079095628</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>6.2739447098032937</v>
+        <v>6.2684016106646983</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>6.7322239147120779</v>
+        <v>6.7262759208567671</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18735,23 +18735,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>5.6265935367864168</v>
+        <v>5.6216223795273716</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>5.8790152368941975</v>
+        <v>5.8738210622875107</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>6.1409364533780426</v>
+        <v>6.1355108684965405</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>6.4126322572440699</v>
+        <v>6.4069666261323208</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>6.9864746306427916</v>
+        <v>6.9803020034842485</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18766,23 +18766,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>5.6212752936163417</v>
+        <v>5.6163088350836157</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>5.915539904839318</v>
+        <v>5.9103134602868819</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>6.2235461857179981</v>
+        <v>6.2180476142296079</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>6.5458240277466331</v>
+        <v>6.5400407202410848</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>7.2353914154700663</v>
+        <v>7.2289988675950712</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18798,23 +18798,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>5.6163165587258286</v>
+        <v>5.6113544812899043</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>5.9499360956314611</v>
+        <v>5.9446792616662441</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>6.3021120850063488</v>
+        <v>6.2965440996820368</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>6.6737378026814955</v>
+        <v>6.66784148194927</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>7.4790861698464166</v>
+        <v>7.4724783149762937</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18829,23 +18829,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>5.6116930296903833</v>
+        <v>5.6067350371932019</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>5.982327846400751</v>
+        <v>5.9770423939675537</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>6.3768321011127522</v>
+        <v>6.3711980998325988</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>6.7965827333881697</v>
+        <v>6.790577877808877</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>7.7176684468582293</v>
+        <v>7.7108498019229472</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18861,23 +18861,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>5.6073820469067535</v>
+        <v>5.6024278632102638</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>6.0128319660063294</v>
+        <v>6.0075195628480405</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>6.4478944940531067</v>
+        <v>6.4421977083673969</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>6.9145596831577514</v>
+        <v>6.9084505936460783</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>7.9512455012753884</v>
+        <v>7.9442204884441452</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18893,23 +18893,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>5.6033624825397315</v>
+        <v>5.5984118501725595</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>6.0415584562642639</v>
+        <v>6.0362206729359595</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>6.5154783083180607</v>
+        <v>6.509721811589305</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>7.0278615556637343</v>
+        <v>7.0216523627018494</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>8.1799223377677137</v>
+        <v>8.1726952864369284</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18925,23 +18925,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>5.5869912108973585</v>
+        <v>5.5820550427286992</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>6.1619481256714028</v>
+        <v>6.1565039767463876</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>6.8068951932580282</v>
+        <v>6.8008812265070455</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>7.5304779247451599</v>
+        <v>7.5238246646944864</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>9.2533267731704232</v>
+        <v>9.245151357217944</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -18957,23 +18957,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>5.5754541307311998</v>
+        <v>5.5705281556997264</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>6.2511162408110543</v>
+        <v>6.245593310875833</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>7.0336356755512952</v>
+        <v>7.0274213810909982</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>7.9410942837474146</v>
+        <v>7.9340782396284784</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>10.218762522942752</v>
+        <v>10.209734133889542</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -18989,23 +18989,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>5.5673237776549103</v>
+        <v>5.5624049858797804</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>6.3171597210923203</v>
+        <v>6.3115784410160645</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>7.2100538893455086</v>
+        <v>7.2036837274534529</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>8.2765505176707386</v>
+        <v>8.2692380942804995</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>11.087089647554242</v>
+        <v>11.077294081938426</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19021,23 +19021,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>5.5615941961496151</v>
+        <v>5.5566804665227467</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>6.3660756511961551</v>
+        <v>6.3604511533577801</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>7.3473182448040371</v>
+        <v>7.340826808344592</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>8.5506041017789212</v>
+        <v>8.5430495490336629</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>11.86807584525188</v>
+        <v>11.857590269742774</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19084,7 +19084,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>8.1799223377677137</v>
+        <v>8.1726952864369284</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19112,7 +19112,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>7.0278615556637343</v>
+        <v>7.0216523627018494</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19140,7 +19140,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>6.5154783083180607</v>
+        <v>6.509721811589305</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19168,7 +19168,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>6.0415584562642639</v>
+        <v>6.0362206729359595</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19196,7 +19196,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>5.6033624825397315</v>
+        <v>5.5984118501725595</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19556,7 +19556,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>7.0278615556637343</v>
+        <v>7.0216523627018494</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19580,7 +19580,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>6.5154783083180607</v>
+        <v>6.509721811589305</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19603,7 +19603,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>6.0415584562642639</v>
+        <v>6.0362206729359595</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19619,7 +19619,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>6.4994749947737462</v>
+        <v>6.4937326371484776</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19666,7 +19666,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>8.1799223377677137</v>
+        <v>8.1726952864369284</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19689,7 +19689,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>5.6033624825397315</v>
+        <v>5.5984118501725595</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19734,7 +19734,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.49</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.19723184159698909</v>
+        <v>0.21026957042132716</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>7.8285352711800131</v>
+        <v>7.8216186741863654</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19765,7 +19765,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>-1.3277324329662294E-2</v>
+        <v>-1.3244673572470986E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19774,7 +19774,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>6.7067364706111396</v>
+        <v>6.7008109951929491</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>6.7083369790990286</v>
+        <v>6.7024100896139895</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19944,7 +19944,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>-5.0702374276051605E-3</v>
+        <v>-5.0702374276051674E-3</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20022,11 +20022,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>3.0526793220806274</v>
+        <v>3.0499822463327027</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>3.5521103644110781</v>
+        <v>3.5494132886631533</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20034,7 +20034,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.4703667901703914</v>
+        <v>0.47030093951173313</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20047,11 +20047,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>3.8812132353073725</v>
+        <v>3.8777841407366602</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>4.4604956427147799</v>
+        <v>4.4570665481440672</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.3349230788684433</v>
+        <v>0.33484669969926129</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20093,11 +20093,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>4.8071230685219506</v>
+        <v>4.8028759224324089</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>5.4705889281550792</v>
+        <v>5.4663417820655376</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20105,7 +20105,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.18431431559490197</v>
+        <v>0.18422683672364426</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20118,11 +20118,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>5.4364993353134707</v>
+        <v>5.4316961283716791</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>6.1549025227860499</v>
+        <v>6.1500993158442583</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>8.2280547363568157E-2</v>
+        <v>8.2185824931304885E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.49</v>
+        <v>4.3499999999999996</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20259,14 +20259,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>12599.264878440001</v>
+        <v>12206.414748599998</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.19723184159698909</v>
+        <v>0.21026957042132716</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20274,13 +20274,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20318,7 +20318,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1454299999999999</v>
+        <v>1.1444179999999999</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20344,7 +20344,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>6.7067364706111396</v>
+        <v>6.7008109951929491</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>361</v>
@@ -20396,7 +20396,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>3.5521103644110781</v>
+        <v>3.5494132886631533</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>439</v>
@@ -20412,7 +20412,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>4.4604956427147799</v>
+        <v>4.4570665481440672</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>440</v>
@@ -20428,7 +20428,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>5.4705889281550792</v>
+        <v>5.4663417820655376</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>442</v>
@@ -20444,7 +20444,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>6.1549025227860499</v>
+        <v>6.1500993158442583</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>441</v>
@@ -20465,22 +20465,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20670,10 +20670,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20689,22 +20689,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20738,7 +20738,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>9.0131305060514755E-2</v>
+        <v>9.2949887826616825E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20748,7 +20748,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>6.1247216035634745E-2</v>
+        <v>6.3218390804597707E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>372</v>
@@ -20839,22 +20839,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>478</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20862,13 +20862,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -20889,7 +20889,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-1.1060927370897773</v>
+        <v>-1.105115491994106</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -20951,7 +20951,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.77400331632749264</v>
+        <v>0.77331947588667704</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -20982,7 +20982,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.29808467449190751</v>
+        <v>0.29782131340429341</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -20995,7 +20995,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>-3.4004746270377105E-2</v>
+        <v>-3.3974702703135441E-2</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21017,33 +21017,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21106,23 +21106,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21140,7 +21140,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>0.86502259539169235</v>
+        <v>0.86425833841698729</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21154,7 +21154,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>7.8285352711800131</v>
+        <v>7.8216186741863654</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21166,13 +21166,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.18 HKD</v>
+        <v>8.17 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21240,7 +21240,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>7.03 HKD</v>
+        <v>7.02 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21262,7 +21262,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>6.52 HKD</v>
+        <v>6.51 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21328,7 +21328,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>6.7067364706111396</v>
+        <v>6.7008109951929491</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21336,13 +21336,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21355,22 +21355,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21435,11 +21435,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>3.0526793220806274</v>
+        <v>3.0499822463327027</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>3.5521103644110781</v>
+        <v>3.5494132886631533</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21456,11 +21456,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>3.8812132353073725</v>
+        <v>3.8777841407366602</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>4.4604956427147799</v>
+        <v>4.4570665481440672</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21496,11 +21496,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>4.8071230685219506</v>
+        <v>4.8028759224324089</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>5.4705889281550792</v>
+        <v>5.4663417820655376</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21517,11 +21517,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>5.4364993353134707</v>
+        <v>5.4316961283716791</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>6.1549025227860499</v>
+        <v>6.1500993158442583</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21539,13 +21539,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21553,13 +21553,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21596,22 +21596,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>387</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21635,15 +21635,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21658,12 +21655,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/1368.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1368.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBEF23EB-391E-4EE8-8086-D87FE0ECF09E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A32A7CF-1E14-4249-8494-737360DC1929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,6 +5025,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5034,16 +5043,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.21026957042132716</v>
+        <v>0.20990734081177126</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>354</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>353</v>
       </c>
       <c r="E16" s="416">
-        <v>1.1444179999999999</v>
+        <v>1.143294</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>6.7008109951929491</v>
+        <v>6.6942297359340106</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>346</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>3.5494132886631533</v>
+        <v>3.5464177223186204</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>405</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>4.4570665481440672</v>
+        <v>4.4532579490358852</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>406</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>5.4663417820655376</v>
+        <v>5.4616245960925687</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>407</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>6.1500993158442583</v>
+        <v>6.1447645286875643</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>408</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>9.2949887826616825E-2</v>
+        <v>9.2858596293350901E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>477</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-1.105115491994106</v>
+        <v>-1.1040300932910085</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.77331947588667704</v>
+        <v>0.77255995349984241</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.29782131340429341</v>
+        <v>0.29752880563504613</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>-3.3974702703135441E-2</v>
+        <v>-3.3941334156119995E-2</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>484</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>482</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>0.86425833841698729</v>
+        <v>0.86340949964271019</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>7.8216186741863654</v>
+        <v>7.8139366040076501</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>490</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.17 HKD</v>
+        <v>8.16 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-2.8103124195484622E-2</v>
+        <v>-2.8067844477660125E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>7.02 HKD</v>
+        <v>7.01 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.4297679529935442E-2</v>
+        <v>2.4336759444308464E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>6.51 HKD</v>
+        <v>6.5 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.1541882125891544E-2</v>
+        <v>5.1583037665035254E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>6.04 HKD</v>
+        <v>6.03 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>7.9489770943233382E-2</v>
+        <v>7.9533128189487476E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>5.6 HKD</v>
+        <v>5.59 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.1081453750105426</v>
+        <v>0.10819106713826274</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>6.7008109951929491</v>
+        <v>6.6942297359340106</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>358</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>3.0499822463327027</v>
+        <v>3.0469866799881697</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>3.5494132886631533</v>
+        <v>3.5464177223186204</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6610,11 +6610,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>3.8777841407366602</v>
+        <v>3.8739755416284782</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>4.4570665481440672</v>
+        <v>4.4532579490358852</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>4.8028759224324089</v>
+        <v>4.79815873645944</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>5.4663417820655376</v>
+        <v>5.4616245960925687</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>5.4316961283716791</v>
+        <v>5.4263613412149851</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>6.1500993158442583</v>
+        <v>6.1447645286875643</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>359</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>437</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,6 +6796,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6812,18 +6824,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -9946,11 +9946,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>4.1609586230548361</v>
+        <v>4.156871901688767</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>0.86425833841698729</v>
+        <v>0.86340949964271019</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10356,11 +10356,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-3101034.0322719999</v>
+        <v>-3097988.324976</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-1.105115491994106</v>
+        <v>-1.1040300932910085</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10373,11 +10373,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>2169990.4036420132</v>
+        <v>2167859.1288685533</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.77331947588667704</v>
+        <v>0.77255995349984241</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10390,11 +10390,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>835708.15457140002</v>
+        <v>834887.3566062001</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.29782131340429341</v>
+        <v>0.29752880563504619</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10407,11 +10407,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>-95335.474058586638</v>
+        <v>-95241.839501246577</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>-3.3974702703135518E-2</v>
+        <v>-3.394133415611994E-2</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -15158,18 +15158,18 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.40433201204578312</v>
+        <v>0.4039348938760764</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.32616825677961953</v>
+        <v>0.3258479078156743</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.35745908448912428</v>
+        <v>0.35710800296911516</v>
       </c>
       <c r="I123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15215,18 +15215,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.2949887826616825E-2</v>
+        <v>9.2858596293350901E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.4981208455084949E-2</v>
+        <v>7.4907565015097544E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.2174502181407885E-2</v>
+        <v>8.2093793786003497E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -16197,7 +16197,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>-3.3974702703135441E-2</v>
+        <v>-3.3941334156119995E-2</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.1444179999999999</v>
+        <v>1.143294</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16247,7 +16247,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>21948027.94080773</v>
+        <v>21926471.496042386</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16269,7 +16269,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>7.8216186741863654</v>
+        <v>7.8139366040076501</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16392,7 +16392,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>6.7024100896139895</v>
+        <v>6.6958272597906863</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18580,23 +18580,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>7.8216186741863654</v>
+        <v>7.8139366040076501</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>7.8216186741863654</v>
+        <v>7.8139366040076501</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>7.8216186741863654</v>
+        <v>7.8139366040076501</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>7.8216186741863654</v>
+        <v>7.8139366040076501</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>7.8216186741863654</v>
+        <v>7.8139366040076501</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18611,23 +18611,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>5.6470184413851925</v>
+        <v>5.6414721735633684</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>5.7038283728260746</v>
+        <v>5.698226308640562</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>5.7606383042669584</v>
+        <v>5.7549804437177574</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>5.8174482357078423</v>
+        <v>5.8117345787949528</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>5.9310680985896083</v>
+        <v>5.9252428489493418</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18642,23 +18642,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>5.6399881468391602</v>
+        <v>5.6344487838817034</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>5.7502271047101452</v>
+        <v>5.7445794696103007</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>5.8615254552420337</v>
+        <v>5.8557685075081709</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>5.9738831984348266</v>
+        <v>5.9680158975753157</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>6.2017768628031167</v>
+        <v>6.1956857342174168</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18673,23 +18673,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>5.6334330936493853</v>
+        <v>5.6279001687939028</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>5.7939219477897836</v>
+        <v>5.7882313974232957</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>5.9574740743511985</v>
+        <v>5.9516228898543018</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>6.1241191066947733</v>
+        <v>6.1181042503434018</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>6.4668064221729811</v>
+        <v>6.4604549925218206</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18704,23 +18704,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>5.6273211559433003</v>
+        <v>5.6217942339801015</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>5.8350704713426342</v>
+        <v>5.829339506599168</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>6.0487259079095628</v>
+        <v>6.0427850996380306</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>6.2684016106646983</v>
+        <v>6.2622450460087888</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>6.7262759208567671</v>
+        <v>6.7196696510016594</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18735,23 +18735,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>5.6216223795273716</v>
+        <v>5.6161010546665358</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>5.8738210622875107</v>
+        <v>5.8680520383172388</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>6.1355108684965405</v>
+        <v>6.1294848236281538</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>6.4069666261323208</v>
+        <v>6.4006739686524732</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>6.9803020034842485</v>
+        <v>6.9734462397231791</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18766,23 +18766,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>5.6163088350836157</v>
+        <v>5.6107927289662411</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>5.9103134602868819</v>
+        <v>5.9045085949934641</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>6.2180476142296079</v>
+        <v>6.2119405051851908</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>6.5400407202410848</v>
+        <v>6.5336173628930272</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>7.2289988675950712</v>
+        <v>7.2218988440659269</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18798,23 +18798,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>5.6113544812899043</v>
+        <v>5.6058432411337993</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>5.9446792616662441</v>
+        <v>5.938840643704876</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>6.2965440996820368</v>
+        <v>6.2903598946380388</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>6.66784148194927</v>
+        <v>6.661292603981857</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>7.4724783149762937</v>
+        <v>7.4651391560098741</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18829,23 +18829,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>5.6067350371932019</v>
+        <v>5.6012283340639222</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>5.9770423939675537</v>
+        <v>5.9711719902769271</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>6.3711980998325988</v>
+        <v>6.3649405727190693</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>6.790577877808877</v>
+        <v>6.7839084532326677</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>7.7108498019229472</v>
+        <v>7.7032765243466068</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18861,23 +18861,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>5.6024278632102638</v>
+        <v>5.5969253904090248</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>6.0075195628480405</v>
+        <v>6.0016192257433811</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>6.4421977083673969</v>
+        <v>6.4358704483765505</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>6.9084505936460783</v>
+        <v>6.9016653993663155</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>7.9442204884441452</v>
+        <v>7.9364180038371126</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18893,23 +18893,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>5.5984118501725595</v>
+        <v>5.592913321733131</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>6.0362206729359595</v>
+        <v>6.0302921467887129</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>6.509721811589305</v>
+        <v>6.5033282322186334</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>7.0216523627018494</v>
+        <v>7.0147559863291633</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>8.1726952864369284</v>
+        <v>8.164668403338311</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18925,23 +18925,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>5.5820550427286992</v>
+        <v>5.576572579268646</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>6.1565039767463876</v>
+        <v>6.1504573133158384</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>6.8008812265070455</v>
+        <v>6.7942016824081302</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>7.5238246646944864</v>
+        <v>7.5164350754682463</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>9.245151357217944</v>
+        <v>9.2360711521481953</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -18957,23 +18957,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>5.5705281556997264</v>
+        <v>5.5650570134710957</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>6.245593310875833</v>
+        <v>6.2394591475880974</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>7.0274213810909982</v>
+        <v>7.0205193386271905</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>7.9340782396284784</v>
+        <v>7.9262857163185156</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>10.209734133889542</v>
+        <v>10.199706555534002</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -18989,23 +18989,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>5.5624049858797804</v>
+        <v>5.5569418218923836</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>6.3115784410160645</v>
+        <v>6.3053794698641763</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>7.2036837274534529</v>
+        <v>7.1966085674073357</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>8.2692380942804995</v>
+        <v>8.2611163908312601</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>11.077294081938426</v>
+        <v>11.066414422104259</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19021,23 +19021,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>5.5566804665227467</v>
+        <v>5.5512229249213645</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>6.3604511533577801</v>
+        <v>6.3542041814503358</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>7.340826808344592</v>
+        <v>7.3336169520398338</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>8.5430495490336629</v>
+        <v>8.5346589193047411</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>11.857590269742774</v>
+        <v>11.845944235284046</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19084,7 +19084,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>8.1726952864369284</v>
+        <v>8.164668403338311</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19112,7 +19112,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>7.0216523627018494</v>
+        <v>7.0147559863291633</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19140,7 +19140,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>6.509721811589305</v>
+        <v>6.5033282322186334</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19168,7 +19168,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>6.0362206729359595</v>
+        <v>6.0302921467887129</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19196,7 +19196,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>5.5984118501725595</v>
+        <v>5.592913321733131</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19556,7 +19556,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>7.0216523627018494</v>
+        <v>7.0147559863291633</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19580,7 +19580,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>6.509721811589305</v>
+        <v>6.5033282322186334</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19603,7 +19603,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>6.0362206729359595</v>
+        <v>6.0302921467887129</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19619,7 +19619,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>6.4937326371484776</v>
+        <v>6.4873547616832585</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19666,7 +19666,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>8.1726952864369284</v>
+        <v>8.164668403338311</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19689,7 +19689,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>5.5984118501725595</v>
+        <v>5.592913321733131</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.21026957042132716</v>
+        <v>0.20990734081177126</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>7.8216186741863654</v>
+        <v>7.8139366040076501</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19765,7 +19765,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>-1.3244673572470986E-2</v>
+        <v>-1.320834162627252E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19774,7 +19774,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>6.7008109951929491</v>
+        <v>6.6942297359340106</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>6.7024100896139895</v>
+        <v>6.6958272597906863</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19944,7 +19944,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>-5.0702374276051674E-3</v>
+        <v>-5.0702374276051466E-3</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20022,11 +20022,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>3.0499822463327027</v>
+        <v>3.0469866799881697</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>3.5494132886631533</v>
+        <v>3.5464177223186204</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20034,7 +20034,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.47030093951173313</v>
+        <v>0.47022766438955987</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20047,11 +20047,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>3.8777841407366602</v>
+        <v>3.8739755416284782</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>4.4570665481440672</v>
+        <v>4.4532579490358852</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.33484669969926129</v>
+        <v>0.33476170900869961</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20093,11 +20093,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>4.8028759224324089</v>
+        <v>4.79815873645944</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>5.4663417820655376</v>
+        <v>5.4616245960925687</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20105,7 +20105,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.18422683672364426</v>
+        <v>0.18412949487301444</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20118,11 +20118,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>5.4316961283716791</v>
+        <v>5.4263613412149851</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>6.1500993158442583</v>
+        <v>6.1447645286875643</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>8.2185824931304885E-2</v>
+        <v>8.2080422829973632E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20266,7 +20266,7 @@
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.21026957042132716</v>
+        <v>0.20990734081177126</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20274,13 +20274,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20318,7 +20318,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.1444179999999999</v>
+        <v>1.143294</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20344,7 +20344,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>6.7008109951929491</v>
+        <v>6.6942297359340106</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>361</v>
@@ -20396,7 +20396,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>3.5494132886631533</v>
+        <v>3.5464177223186204</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>439</v>
@@ -20412,7 +20412,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>4.4570665481440672</v>
+        <v>4.4532579490358852</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>440</v>
@@ -20428,7 +20428,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>5.4663417820655376</v>
+        <v>5.4616245960925687</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>442</v>
@@ -20444,7 +20444,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>6.1500993158442583</v>
+        <v>6.1447645286875643</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>441</v>
@@ -20465,22 +20465,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20670,10 +20670,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20689,22 +20689,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20738,7 +20738,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>9.2949887826616825E-2</v>
+        <v>9.2858596293350901E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20839,22 +20839,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>478</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20862,13 +20862,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -20889,7 +20889,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-1.105115491994106</v>
+        <v>-1.1040300932910085</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -20951,7 +20951,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.77331947588667704</v>
+        <v>0.77255995349984241</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -20982,7 +20982,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.29782131340429341</v>
+        <v>0.29752880563504613</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -20995,7 +20995,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>-3.3974702703135441E-2</v>
+        <v>-3.3941334156119995E-2</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21017,33 +21017,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21106,23 +21106,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21140,7 +21140,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>0.86425833841698729</v>
+        <v>0.86340949964271019</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21154,7 +21154,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>7.8216186741863654</v>
+        <v>7.8139366040076501</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21166,13 +21166,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.17 HKD</v>
+        <v>8.16 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21240,7 +21240,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>7.02 HKD</v>
+        <v>7.01 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21262,7 +21262,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>6.51 HKD</v>
+        <v>6.5 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21284,7 +21284,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>6.04 HKD</v>
+        <v>6.03 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21306,7 +21306,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>5.6 HKD</v>
+        <v>5.59 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21328,7 +21328,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>6.7008109951929491</v>
+        <v>6.6942297359340106</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21336,13 +21336,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21355,22 +21355,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21435,11 +21435,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>3.0499822463327027</v>
+        <v>3.0469866799881697</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>3.5494132886631533</v>
+        <v>3.5464177223186204</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21456,11 +21456,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>3.8777841407366602</v>
+        <v>3.8739755416284782</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>4.4570665481440672</v>
+        <v>4.4532579490358852</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21496,11 +21496,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>4.8028759224324089</v>
+        <v>4.79815873645944</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>5.4663417820655376</v>
+        <v>5.4616245960925687</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21517,11 +21517,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>5.4316961283716791</v>
+        <v>5.4263613412149851</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>6.1500993158442583</v>
+        <v>6.1447645286875643</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21539,13 +21539,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21553,13 +21553,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21596,22 +21596,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>387</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21635,12 +21635,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21655,15 +21658,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/1368.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1368.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A32A7CF-1E14-4249-8494-737360DC1929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F1487C-64CF-4669-B4D9-F8BD6DD48ECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,25 +5025,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>349</v>
       </c>
       <c r="C8" s="47">
-        <v>4.3499999999999996</v>
+        <v>4.41</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>12206.414748599998</v>
+        <v>12374.77908996</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.20990734081177126</v>
+        <v>0.20452956926823004</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>354</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>353</v>
       </c>
       <c r="E16" s="416">
-        <v>1.143294</v>
+        <v>1.1445970000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>6.6942297359340106</v>
+        <v>6.7018590782955743</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>346</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>3.5464177223186204</v>
+        <v>3.5498903405988043</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>405</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>4.4532579490358852</v>
+        <v>4.4576730777173461</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>406</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>5.4616245960925687</v>
+        <v>5.4670930065220871</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>407</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>6.1447645286875643</v>
+        <v>6.1509488949377173</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>408</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>9.2858596293350901E-2</v>
+        <v>9.169960412114124E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.3218390804597707E-2</v>
+        <v>6.2358276643990934E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>477</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-1.1040300932910085</v>
+        <v>-1.1052883446345458</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.77255995349984241</v>
+        <v>0.77344043185397549</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.29752880563504613</v>
+        <v>0.29786789604726077</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>-3.3941334156119995E-2</v>
+        <v>-3.3980016733309616E-2</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>482</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>0.86340949964271019</v>
+        <v>0.86439351825737498</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>7.8139366040076501</v>
+        <v>7.8228420643660721</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>490</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.16 HKD</v>
+        <v>8.17 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-2.8067844477660125E-2</v>
+        <v>-2.810873619899738E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>7.01 HKD</v>
+        <v>7.02 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.4336759444308464E-2</v>
+        <v>2.4291463031341949E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>6.5 HKD</v>
+        <v>6.51 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.1583037665035254E-2</v>
+        <v>5.1535335459473218E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>6.03 HKD</v>
+        <v>6.04 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>7.9533128189487476E-2</v>
+        <v>7.9482874053646721E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>5.59 HKD</v>
+        <v>5.6 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.10819106713826274</v>
+        <v>0.10813810671440066</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>356</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>6.6942297359340106</v>
+        <v>6.7018590782955743</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>358</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>3.0469866799881697</v>
+        <v>3.0504592982683536</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>3.5464177223186204</v>
+        <v>3.5498903405988043</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6610,11 +6610,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>3.8739755416284782</v>
+        <v>3.8783906703099387</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>4.4532579490358852</v>
+        <v>4.4576730777173461</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>4.79815873645944</v>
+        <v>4.8036271468889584</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>5.4616245960925687</v>
+        <v>5.4670930065220871</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>5.4263613412149851</v>
+        <v>5.4325457074651382</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>6.1447645286875643</v>
+        <v>6.1509488949377173</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>437</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,18 +6796,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6824,6 +6812,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -9946,11 +9946,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>4.156871901688767</v>
+        <v>4.1616094443400025</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>0.86340949964271019</v>
+        <v>0.86439351825737498</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10356,11 +10356,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-3097988.324976</v>
+        <v>-3101519.0692880005</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-1.1040300932910085</v>
+        <v>-1.1052883446345461</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10373,11 +10373,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>2167859.1288685533</v>
+        <v>2170329.8148381426</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.77255995349984241</v>
+        <v>0.77344043185397549</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10390,11 +10390,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>834887.3566062001</v>
+        <v>835838.86883810011</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.29752880563504619</v>
+        <v>0.29786789604726077</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10407,11 +10407,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>-95241.839501246577</v>
+        <v>-95350.385611757752</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>-3.394133415611994E-2</v>
+        <v>-3.3980016733309804E-2</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -13994,16 +13994,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.3218390804597707E-2</v>
+        <v>6.2358276643990934E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.3218390804597707E-2</v>
+        <v>6.2358276643990934E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.7701149425287361E-2</v>
+        <v>5.6916099773242627E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15158,18 +15158,18 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.4039348938760764</v>
+        <v>0.40439525417423294</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.3258479078156743</v>
+        <v>0.32621927320715177</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.35710800296911516</v>
+        <v>0.35751499515823609</v>
       </c>
       <c r="I123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15215,18 +15215,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.2858596293350901E-2</v>
+        <v>9.169960412114124E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.4907565015097544E-2</v>
+        <v>7.3972624310011739E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>8.2093793786003497E-2</v>
+        <v>8.106915989982677E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15272,11 +15272,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11236477116733322</v>
+        <v>0.11083599877049873</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.106952289176454</v>
+        <v>0.10549715599037977</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16197,7 +16197,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>-3.3941334156119995E-2</v>
+        <v>-3.3980016733309616E-2</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>1.143294</v>
+        <v>1.1445970000000001</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16247,7 +16247,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>21926471.496042386</v>
+        <v>21951460.862171609</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16269,7 +16269,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>7.8139366040076501</v>
+        <v>7.8228420643660721</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16392,7 +16392,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>6.6958272597906863</v>
+        <v>6.7034584228331813</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18580,23 +18580,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>7.8139366040076501</v>
+        <v>7.8228420643660721</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>7.8139366040076501</v>
+        <v>7.8228420643660721</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>7.8139366040076501</v>
+        <v>7.8228420643660721</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>7.8139366040076501</v>
+        <v>7.8228420643660721</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>7.8139366040076501</v>
+        <v>7.8228420643660721</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18611,23 +18611,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>5.6414721735633684</v>
+        <v>5.6479016993390241</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>5.698226308640562</v>
+        <v>5.704720516499747</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>5.7549804437177574</v>
+        <v>5.7615393336604708</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>5.8117345787949528</v>
+        <v>5.8183581508211946</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>5.9252428489493418</v>
+        <v>5.9319957851426413</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18642,23 +18642,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>5.6344487838817034</v>
+        <v>5.6408703051749125</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>5.7445794696103007</v>
+        <v>5.7511265056735557</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>5.8557685075081709</v>
+        <v>5.8624422645341703</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>5.9680158975753157</v>
+        <v>5.9748175817567599</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>6.1956857342174168</v>
+        <v>6.2027468912878509</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18673,23 +18673,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>5.6279001687939028</v>
+        <v>5.634314226700214</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>5.7882313974232957</v>
+        <v>5.7948281831239496</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>5.9516228898543018</v>
+        <v>5.9584058910993711</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>6.1181042503434018</v>
+        <v>6.1250769886226175</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>6.4604549925218206</v>
+        <v>6.467817904297144</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18704,23 +18704,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>5.6217942339801015</v>
+        <v>5.6282013330175111</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>5.829339506599168</v>
+        <v>5.8359831427742019</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>6.0427850996380306</v>
+        <v>6.0496719974830544</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>6.2622450460087888</v>
+        <v>6.2693820600182653</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>6.7196696510016594</v>
+        <v>6.7273279869635862</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18735,23 +18735,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>5.6161010546665358</v>
+        <v>5.6225016652480928</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>5.8680520383172388</v>
+        <v>5.8747397947525286</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>6.1294848236281538</v>
+        <v>6.1364705322255819</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>6.4006739686524732</v>
+        <v>6.4079687486313368</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>6.9734462397231791</v>
+        <v>6.9813938021615014</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18766,23 +18766,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>5.6107927289662411</v>
+        <v>5.6171872897055115</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>5.9045085949934641</v>
+        <v>5.9112379005782714</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>6.2119405051851908</v>
+        <v>6.2190201876450448</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>6.5336173628930272</v>
+        <v>6.5410636570429563</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>7.2218988440659269</v>
+        <v>7.2301295652923292</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18798,23 +18798,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>5.6058432411337993</v>
+        <v>5.6122321609944805</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>5.938840643704876</v>
+        <v>5.9456090771600918</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>6.2903598946380388</v>
+        <v>6.2975289508411798</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>6.661292603981857</v>
+        <v>6.6688844082447929</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>7.4651391560098741</v>
+        <v>7.4736470956302004</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18829,23 +18829,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>5.6012283340639222</v>
+        <v>5.6076119943641469</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>5.9711719902769271</v>
+        <v>5.9779772714236241</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>6.3649405727190693</v>
+        <v>6.3721946277270138</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>6.7839084532326677</v>
+        <v>6.7916400014735947</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>7.7032765243466068</v>
+        <v>7.7120558665903545</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18861,23 +18861,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>5.5969253904090248</v>
+        <v>5.603304146690177</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>6.0016192257433811</v>
+        <v>6.0084592072801897</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>6.4358704483765505</v>
+        <v>6.4432053414086452</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>6.9016653993663155</v>
+        <v>6.909531153945081</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>7.9364180038371126</v>
+        <v>7.9454630549429526</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18893,23 +18893,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>5.592913321733131</v>
+        <v>5.5992875055023266</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>6.0302921467887129</v>
+        <v>6.0371648065483781</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>6.5033282322186334</v>
+        <v>6.510740006168799</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>7.0147559863291633</v>
+        <v>7.0227506290458992</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>8.164668403338311</v>
+        <v>8.1739735889944498</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18925,23 +18925,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>5.576572579268646</v>
+        <v>5.5829281396676231</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>6.1504573133158384</v>
+        <v>6.157466924036485</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>6.7942016824081302</v>
+        <v>6.8019449617327634</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>7.5164350754682463</v>
+        <v>7.5250014765018696</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>9.2360711521481953</v>
+        <v>9.2465974041107266</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -18957,23 +18957,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>5.5650570134710957</v>
+        <v>5.57139944970233</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>6.2394591475880974</v>
+        <v>6.2465701927517276</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>7.0205193386271905</v>
+        <v>7.0285205497751821</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>7.9262857163185156</v>
+        <v>7.9353192197641409</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>10.199706555534002</v>
+        <v>10.211331052506662</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -18989,23 +18989,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>5.5569418218923836</v>
+        <v>5.5632750093261727</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>6.3053794698641763</v>
+        <v>6.3125656437173001</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>7.1966085674073357</v>
+        <v>7.2048104655746767</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>8.2611163908312601</v>
+        <v>8.2705314972319357</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>11.066414422104259</v>
+        <v>11.079026696805256</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19021,23 +19021,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>5.5512229249213645</v>
+        <v>5.55754959458916</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>6.3542041814503358</v>
+        <v>6.3614460003074536</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>7.3336169520398338</v>
+        <v>7.3419749972045141</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>8.5346589193047411</v>
+        <v>8.5443857792129148</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>11.845944235284046</v>
+        <v>11.859444931814052</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19084,7 +19084,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>8.164668403338311</v>
+        <v>8.1739735889944498</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19112,7 +19112,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>7.0147559863291633</v>
+        <v>7.0227506290458992</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19140,7 +19140,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>6.5033282322186334</v>
+        <v>6.510740006168799</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19168,7 +19168,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>6.0302921467887129</v>
+        <v>6.0371648065483781</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19196,7 +19196,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>5.592913321733131</v>
+        <v>5.5992875055023266</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19556,7 +19556,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>7.0147559863291633</v>
+        <v>7.0227506290458992</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19580,7 +19580,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>6.5033282322186334</v>
+        <v>6.510740006168799</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19603,7 +19603,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>6.0302921467887129</v>
+        <v>6.0371648065483781</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19619,7 +19619,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>6.4873547616832585</v>
+        <v>6.4947483308391138</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19666,7 +19666,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>8.164668403338311</v>
+        <v>8.1739735889944498</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19689,7 +19689,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>5.592913321733131</v>
+        <v>5.5992875055023266</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19734,7 +19734,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.3499999999999996</v>
+        <v>4.41</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.20990734081177126</v>
+        <v>0.20452956926823004</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>7.8139366040076501</v>
+        <v>7.8228420643660721</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19765,7 +19765,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>-1.320834162627252E-2</v>
+        <v>-1.325045295349455E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19774,7 +19774,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>6.6942297359340106</v>
+        <v>6.7018590782955743</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>6.6958272597906863</v>
+        <v>6.7034584228331813</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19944,7 +19944,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>-5.0702374276051466E-3</v>
+        <v>-5.0702374276051839E-3</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20022,11 +20022,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>3.0469866799881697</v>
+        <v>3.0504592982683536</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>3.5464177223186204</v>
+        <v>3.5498903405988043</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20034,7 +20034,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.47022766438955987</v>
+        <v>0.47031259548632331</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20047,11 +20047,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>3.8739755416284782</v>
+        <v>3.8783906703099387</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>4.4532579490358852</v>
+        <v>4.4576730777173461</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.33476170900869961</v>
+        <v>0.33486021928544829</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20093,11 +20093,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>4.79815873645944</v>
+        <v>4.8036271468889584</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>5.4616245960925687</v>
+        <v>5.4670930065220871</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20105,7 +20105,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.18412949487301444</v>
+        <v>0.1842423210258719</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20118,11 +20118,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>5.4263613412149851</v>
+        <v>5.4325457074651382</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>6.1447645286875643</v>
+        <v>6.1509488949377173</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>8.2080422829973632E-2</v>
+        <v>8.2202591388711332E-2</v>
       </c>
     </row>
   </sheetData>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.3499999999999996</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20259,14 +20259,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>12206.414748599998</v>
+        <v>12374.77908996</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.20990734081177126</v>
+        <v>0.20452956926823004</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20274,13 +20274,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20318,7 +20318,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>1.143294</v>
+        <v>1.1445970000000001</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20344,7 +20344,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>6.6942297359340106</v>
+        <v>6.7018590782955743</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>361</v>
@@ -20396,7 +20396,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>3.5464177223186204</v>
+        <v>3.5498903405988043</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>439</v>
@@ -20412,7 +20412,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>4.4532579490358852</v>
+        <v>4.4576730777173461</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>440</v>
@@ -20428,7 +20428,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>5.4616245960925687</v>
+        <v>5.4670930065220871</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>442</v>
@@ -20444,7 +20444,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>6.1447645286875643</v>
+        <v>6.1509488949377173</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>441</v>
@@ -20465,22 +20465,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20670,10 +20670,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20689,22 +20689,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20738,7 +20738,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>9.2858596293350901E-2</v>
+        <v>9.169960412114124E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20748,7 +20748,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>6.3218390804597707E-2</v>
+        <v>6.2358276643990934E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>372</v>
@@ -20839,22 +20839,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>478</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20862,13 +20862,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -20889,7 +20889,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-1.1040300932910085</v>
+        <v>-1.1052883446345458</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -20951,7 +20951,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.77255995349984241</v>
+        <v>0.77344043185397549</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -20982,7 +20982,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.29752880563504613</v>
+        <v>0.29786789604726077</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -20995,7 +20995,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>-3.3941334156119995E-2</v>
+        <v>-3.3980016733309616E-2</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21017,33 +21017,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21106,23 +21106,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21140,7 +21140,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>0.86340949964271019</v>
+        <v>0.86439351825737498</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21154,7 +21154,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>7.8139366040076501</v>
+        <v>7.8228420643660721</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21166,13 +21166,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21217,7 +21217,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>8.16 HKD</v>
+        <v>8.17 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21240,7 +21240,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>7.01 HKD</v>
+        <v>7.02 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21262,7 +21262,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>6.5 HKD</v>
+        <v>6.51 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21284,7 +21284,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>6.03 HKD</v>
+        <v>6.04 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21306,7 +21306,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>5.59 HKD</v>
+        <v>5.6 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21328,7 +21328,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>6.6942297359340106</v>
+        <v>6.7018590782955743</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21336,13 +21336,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21355,22 +21355,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21435,11 +21435,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>3.0469866799881697</v>
+        <v>3.0504592982683536</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>3.5464177223186204</v>
+        <v>3.5498903405988043</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21456,11 +21456,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>3.8739755416284782</v>
+        <v>3.8783906703099387</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>4.4532579490358852</v>
+        <v>4.4576730777173461</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21496,11 +21496,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>4.79815873645944</v>
+        <v>4.8036271468889584</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>5.4616245960925687</v>
+        <v>5.4670930065220871</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21517,11 +21517,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>5.4263613412149851</v>
+        <v>5.4325457074651382</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>6.1447645286875643</v>
+        <v>6.1509488949377173</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21539,13 +21539,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21553,13 +21553,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21596,22 +21596,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>387</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21635,15 +21635,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21658,12 +21655,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
